--- a/textos/CONTROL DE CAMBIOS APARTIR DE LA 6.3.1.xlsx
+++ b/textos/CONTROL DE CAMBIOS APARTIR DE LA 6.3.1.xlsx
@@ -1,31 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\HOME OFFICE\ERP- COMEGCEN - SEMUBI - FLOR\ERP - SISC\ERP\textos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\HOME OFFICE\ERP- COMEGCEN - SEMUBI - FLOR\ERP - SISC\ERP\textos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11AAD801-176E-470F-9ED6-5E608222028E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{198C48CE-B3DE-4893-B426-5BF5CB7411DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="50">
   <si>
     <t xml:space="preserve">CONTRO DE CAMBIOS DE ERP SISC </t>
   </si>
@@ -58,13 +70,140 @@
   </si>
   <si>
     <t>carga de lista tipos de articulos</t>
+  </si>
+  <si>
+    <t>M_repor_iven</t>
+  </si>
+  <si>
+    <t>Reportes de impuestos  ventas  compras</t>
+  </si>
+  <si>
+    <t>new!</t>
+  </si>
+  <si>
+    <t>W_Fecha_impuestos</t>
+  </si>
+  <si>
+    <t>R_libro_ventas_isv</t>
+  </si>
+  <si>
+    <t>reporte para ventas con impuestos</t>
+  </si>
+  <si>
+    <t>filtro de fechas y selecciob de impuestos</t>
+  </si>
+  <si>
+    <t>R_libro_compras_isv</t>
+  </si>
+  <si>
+    <t>reporte para compras con impuestos</t>
+  </si>
+  <si>
+    <t>w_bod_deatalle_s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">quiza asinganr los importes </t>
+  </si>
+  <si>
+    <t>R_Comprob_Entrega_ESMUGRUPAL</t>
+  </si>
+  <si>
+    <t>asignacion de valores según impuestos</t>
+  </si>
+  <si>
+    <t>calculo impuestos</t>
+  </si>
+  <si>
+    <t>se traslado la ventan ade paramtros por empresa</t>
+  </si>
+  <si>
+    <t>w_parametros_x_empresa</t>
+  </si>
+  <si>
+    <t>para editar e ingresar paramtros x empresa</t>
+  </si>
+  <si>
+    <t>W_Ingr_Par_X_Empresa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">file </t>
+  </si>
+  <si>
+    <t xml:space="preserve">file IMPUESTOS </t>
+  </si>
+  <si>
+    <t>un fiele para guaradar la matrios de impuestos</t>
+  </si>
+  <si>
+    <t>STARTUP</t>
+  </si>
+  <si>
+    <t>FUNISON QUE VALIDA PARAMTROS ISV</t>
+  </si>
+  <si>
+    <t>OBSERVACION</t>
+  </si>
+  <si>
+    <t>se debe tomar en cuenta que si cambia el tipo de producto la factura se calcualra en base a ese tipo en la factura</t>
+  </si>
+  <si>
+    <t>se modifico el trigger  trg_PagosF_Aju_Sald</t>
+  </si>
+  <si>
+    <t>trigger</t>
+  </si>
+  <si>
+    <t>se debe actualiza el trigger para que no tome en cuenta el saldo en vales</t>
+  </si>
+  <si>
+    <t>r_comprob_entrega_comgecen</t>
+  </si>
+  <si>
+    <t>mejora al caluclo de rebajas</t>
+  </si>
+  <si>
+    <t>sub total</t>
+  </si>
+  <si>
+    <t>F_Variables.MONTO2</t>
+  </si>
+  <si>
+    <t>descuento</t>
+  </si>
+  <si>
+    <t>F_Variables.MONTO3</t>
+  </si>
+  <si>
+    <t>F_Variables.MONTO4</t>
+  </si>
+  <si>
+    <t>impuesto</t>
+  </si>
+  <si>
+    <t>F_Variables.MONTO5</t>
+  </si>
+  <si>
+    <t>total</t>
+  </si>
+  <si>
+    <t>la cuenta contable de la aprtida asignada al 15% alamacenara tambien el de 18% ojo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -111,17 +250,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Millares" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -400,108 +544,110 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M36"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="5" customWidth="1"/>
-    <col min="3" max="3" width="48.21875" customWidth="1"/>
-    <col min="4" max="4" width="39.33203125" customWidth="1"/>
-    <col min="5" max="5" width="10.33203125" customWidth="1"/>
+    <col min="3" max="3" width="48.28515625" customWidth="1"/>
+    <col min="4" max="4" width="39.28515625" customWidth="1"/>
+    <col min="5" max="5" width="10.28515625" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>1</v>
       </c>
@@ -515,9 +661,11 @@
       <c r="E7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="1"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F7" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -528,7 +676,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6.4</v>
       </c>
@@ -542,7 +690,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
         <v>9</v>
       </c>
@@ -552,8 +700,9 @@
       <c r="E10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
         <v>10</v>
       </c>
@@ -563,6 +712,204 @@
       <c r="E11">
         <v>100</v>
       </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12">
+        <v>10</v>
+      </c>
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16">
+        <v>471</v>
+      </c>
+      <c r="F16" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16" s="2"/>
+    </row>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C25" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="5">
+        <v>200204</v>
+      </c>
+      <c r="F25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="H31" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="I31" t="s">
+        <v>42</v>
+      </c>
+      <c r="M31" s="2"/>
+    </row>
+    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="H32" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I32" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H33" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I33" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H34" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I34" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="35" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H35" s="4"/>
+    </row>
+    <row r="36" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H36" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/textos/CONTROL DE CAMBIOS APARTIR DE LA 6.3.1.xlsx
+++ b/textos/CONTROL DE CAMBIOS APARTIR DE LA 6.3.1.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\HOME OFFICE\ERP- COMEGCEN - SEMUBI - FLOR\ERP - SISC\ERP\textos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\HOME OFFICE\ERP- COMEGCEN - SEMUBI - FLOR\ERP - SISC\ERP\textos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{198C48CE-B3DE-4893-B426-5BF5CB7411DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C0A580-48CC-4C24-945E-BF1CF5BD5D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="CAMBIOS" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
+    <sheet name="Hoja3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,15 +31,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="139">
   <si>
     <t xml:space="preserve">CONTRO DE CAMBIOS DE ERP SISC </t>
   </si>
@@ -187,16 +186,284 @@
   </si>
   <si>
     <t>la cuenta contable de la aprtida asignada al 15% alamacenara tambien el de 18% ojo</t>
+  </si>
+  <si>
+    <t>6.4.2</t>
+  </si>
+  <si>
+    <t>mejora orden de compra listado s de tipos para traer el impuesto</t>
+  </si>
+  <si>
+    <t>para buscar el tipo de producto y traer su impuesto</t>
+  </si>
+  <si>
+    <t>agregado formatos de recibos</t>
+  </si>
+  <si>
+    <t>w_cai</t>
+  </si>
+  <si>
+    <t>reporte existencias por fecha</t>
+  </si>
+  <si>
+    <t>6,70</t>
+  </si>
+  <si>
+    <t>periodo</t>
+  </si>
+  <si>
+    <t>aCUM</t>
+  </si>
+  <si>
+    <t>a fecha</t>
+  </si>
+  <si>
+    <t>W_ORDEN_COMPRA</t>
+  </si>
+  <si>
+    <t>Correcion partida reversion ordend de compra</t>
+  </si>
+  <si>
+    <t>se dejo la partida de reversion dentro de la misma partida</t>
+  </si>
+  <si>
+    <t>M_subpro_cxp</t>
+  </si>
+  <si>
+    <t>proceso de mantenimiento de registros cxp,ordenenes de compra</t>
+  </si>
+  <si>
+    <t>m_ctas_pag</t>
+  </si>
+  <si>
+    <t>agregado subproceso cxp</t>
+  </si>
+  <si>
+    <t>W_CXP_NO_COMPLETAS</t>
+  </si>
+  <si>
+    <t>MUESTRA LAS CXP QUE NO TIENEN DETALLE DE PARTIDA</t>
+  </si>
+  <si>
+    <t>BDS_COD_PROD</t>
+  </si>
+  <si>
+    <t>sum(F_Bod_Det_S.BDS_CANT)</t>
+  </si>
+  <si>
+    <t>BDS_COSTO</t>
+  </si>
+  <si>
+    <t>'310000085'</t>
+  </si>
+  <si>
+    <t>'310000082'</t>
+  </si>
+  <si>
+    <t>'310000081'</t>
+  </si>
+  <si>
+    <t>'310000080'</t>
+  </si>
+  <si>
+    <t>'310000079'</t>
+  </si>
+  <si>
+    <t>'310000078'</t>
+  </si>
+  <si>
+    <t>'310000077'</t>
+  </si>
+  <si>
+    <t>'310000076'</t>
+  </si>
+  <si>
+    <t>'310000075'</t>
+  </si>
+  <si>
+    <t>'310000071'</t>
+  </si>
+  <si>
+    <t>'310000069'</t>
+  </si>
+  <si>
+    <t>'310000066'</t>
+  </si>
+  <si>
+    <t>'310000065'</t>
+  </si>
+  <si>
+    <t>'310000059'</t>
+  </si>
+  <si>
+    <t>'310000058'</t>
+  </si>
+  <si>
+    <t>'310000056'</t>
+  </si>
+  <si>
+    <t>'310000055'</t>
+  </si>
+  <si>
+    <t>'310000054'</t>
+  </si>
+  <si>
+    <t>'310000053'</t>
+  </si>
+  <si>
+    <t>'310000051'</t>
+  </si>
+  <si>
+    <t>'310000050'</t>
+  </si>
+  <si>
+    <t>'310000045'</t>
+  </si>
+  <si>
+    <t>'310000042'</t>
+  </si>
+  <si>
+    <t>'310000038'</t>
+  </si>
+  <si>
+    <t>'310000036'</t>
+  </si>
+  <si>
+    <t>'310000035'</t>
+  </si>
+  <si>
+    <t>'310000033'</t>
+  </si>
+  <si>
+    <t>'310000026'</t>
+  </si>
+  <si>
+    <t>'310000024'</t>
+  </si>
+  <si>
+    <t>'310000020'</t>
+  </si>
+  <si>
+    <t>'310000018'</t>
+  </si>
+  <si>
+    <t>'310000017'</t>
+  </si>
+  <si>
+    <t>'310000016'</t>
+  </si>
+  <si>
+    <t>'310000014'</t>
+  </si>
+  <si>
+    <t>'310000013'</t>
+  </si>
+  <si>
+    <t>'310000012'</t>
+  </si>
+  <si>
+    <t>'310000011'</t>
+  </si>
+  <si>
+    <t>'310000010'</t>
+  </si>
+  <si>
+    <t>'310000009'</t>
+  </si>
+  <si>
+    <t>'310000006'</t>
+  </si>
+  <si>
+    <t>'310000005'</t>
+  </si>
+  <si>
+    <t>'310000004'</t>
+  </si>
+  <si>
+    <t>'310000003'</t>
+  </si>
+  <si>
+    <t>'310000002'</t>
+  </si>
+  <si>
+    <t>'310000001'</t>
+  </si>
+  <si>
+    <t>REDMIEN #14364</t>
+  </si>
+  <si>
+    <t>ARREGLO REPORTE LIBRO DE VENTAS Y COMPRAS, TOTALES no cuadraban</t>
+  </si>
+  <si>
+    <t>codigo</t>
+  </si>
+  <si>
+    <t>FECHA</t>
+  </si>
+  <si>
+    <t>TIPO</t>
+  </si>
+  <si>
+    <t>bde_CANT</t>
+  </si>
+  <si>
+    <t>costo</t>
+  </si>
+  <si>
+    <t>'2025-12-31'</t>
+  </si>
+  <si>
+    <t>'E'</t>
+  </si>
+  <si>
+    <t>'2026-01-09'</t>
+  </si>
+  <si>
+    <t>'S'</t>
+  </si>
+  <si>
+    <t>'2026-01-22'</t>
+  </si>
+  <si>
+    <t>'2026-02-05'</t>
+  </si>
+  <si>
+    <t>'2026-02-10'</t>
+  </si>
+  <si>
+    <t>'2026-02-12'</t>
+  </si>
+  <si>
+    <t>'2026-02-16'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTROS PARA REPORTE fecha dos </t>
+  </si>
+  <si>
+    <t>R_entradas</t>
+  </si>
+  <si>
+    <t>se cambio filtro de fechas</t>
+  </si>
+  <si>
+    <t>encabezado</t>
+  </si>
+  <si>
+    <t>R_Existencia_Fecha2</t>
+  </si>
+  <si>
+    <t>nuevo reporte de existencias por fehca</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="44" formatCode="_-&quot;L&quot;* #,##0.00_-;\-&quot;L&quot;* #,##0.00_-;_-&quot;L&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -211,8 +478,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -225,8 +500,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -249,23 +530,52 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
+    <cellStyle name="Moneda" xfId="2" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -544,110 +854,111 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P113"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="5" customWidth="1"/>
-    <col min="3" max="3" width="48.28515625" customWidth="1"/>
-    <col min="4" max="4" width="39.28515625" customWidth="1"/>
-    <col min="5" max="5" width="10.28515625" customWidth="1"/>
-    <col min="6" max="6" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" customWidth="1"/>
+    <col min="3" max="3" width="48.33203125" customWidth="1"/>
+    <col min="4" max="4" width="39.33203125" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" customWidth="1"/>
+    <col min="6" max="6" width="22.21875" customWidth="1"/>
+    <col min="8" max="8" width="13.109375" customWidth="1"/>
+    <col min="14" max="14" width="12.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>1</v>
       </c>
@@ -665,10 +976,11 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>5</v>
       </c>
+      <c r="C8" s="5"/>
       <c r="D8" t="s">
         <v>6</v>
       </c>
@@ -676,11 +988,11 @@
         <v>440</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>6.4</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D9" t="s">
@@ -690,8 +1002,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C10" t="s">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D10" t="s">
@@ -702,8 +1014,8 @@
       </c>
       <c r="H10" s="2"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C11" t="s">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C11" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D11" t="s">
@@ -713,8 +1025,8 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C12" t="s">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C12" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D12" t="s">
@@ -725,11 +1037,11 @@
       </c>
       <c r="H12" s="2"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>13</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D13" t="s">
@@ -737,11 +1049,11 @@
       </c>
       <c r="H13" s="2"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>13</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="5" t="s">
         <v>16</v>
       </c>
       <c r="D14" t="s">
@@ -749,11 +1061,11 @@
       </c>
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>13</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D15" t="s">
@@ -761,8 +1073,8 @@
       </c>
       <c r="H15" s="2"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C16" t="s">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C16" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D16" t="s">
@@ -776,16 +1088,16 @@
       </c>
       <c r="H16" s="2"/>
     </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C17" t="s">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C17" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D17" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C18" t="s">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C18" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D18" t="s">
@@ -795,30 +1107,30 @@
         <v>367</v>
       </c>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>13</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="5" t="s">
         <v>25</v>
       </c>
       <c r="D19" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C20" t="s">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C20" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D20" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>13</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="5" t="s">
         <v>31</v>
       </c>
       <c r="D21" t="s">
@@ -828,8 +1140,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C22" t="s">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C22" s="5" t="s">
         <v>33</v>
       </c>
       <c r="D22" t="s">
@@ -839,8 +1151,8 @@
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C23" t="s">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C23" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D23" t="s">
@@ -850,66 +1162,496 @@
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C24" t="s">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C24" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D24" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C25" t="s">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C25" s="5" t="s">
         <v>40</v>
       </c>
       <c r="D25" t="s">
         <v>20</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E25" s="4">
         <v>200204</v>
       </c>
       <c r="F25" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="H31" s="4" t="s">
+    <row r="26" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D26" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26">
+        <v>101</v>
+      </c>
+      <c r="F26" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C27" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D27" t="s">
+        <v>54</v>
+      </c>
+      <c r="E27" s="4">
+        <v>15101</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C28" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C29" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E29" s="4">
+        <v>266265</v>
+      </c>
+      <c r="F29" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D30" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C31" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D31" t="s">
+        <v>65</v>
+      </c>
+      <c r="E31">
+        <v>15</v>
+      </c>
+      <c r="M31" s="2"/>
+    </row>
+    <row r="32" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B32" t="s">
+        <v>13</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C33" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" s="4">
+        <v>366367</v>
+      </c>
+      <c r="F33" t="s">
+        <v>117</v>
+      </c>
+      <c r="O33" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="I31" t="s">
+      <c r="P33" t="s">
         <v>42</v>
       </c>
-      <c r="M31" s="2"/>
-    </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="H32" s="4" t="s">
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C34" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="O34" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="I32" t="s">
+      <c r="P34" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="33" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H33" s="4" t="s">
+    <row r="35" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C35" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="D35" t="s">
+        <v>134</v>
+      </c>
+      <c r="E35" t="s">
+        <v>135</v>
+      </c>
+      <c r="H35" s="3"/>
+      <c r="O35" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="I33" t="s">
+      <c r="P35" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="34" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H34" s="4" t="s">
+    <row r="36" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D36" t="s">
+        <v>137</v>
+      </c>
+      <c r="H36" s="3"/>
+      <c r="O36" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="I34" t="s">
+      <c r="P36" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="35" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H35" s="4"/>
-    </row>
-    <row r="36" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H36" s="4"/>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D40" s="2"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D41" s="2"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D42" s="2"/>
+    </row>
+    <row r="55" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="N55">
+        <v>145140</v>
+      </c>
+    </row>
+    <row r="56" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="N56">
+        <v>63282</v>
+      </c>
+    </row>
+    <row r="57" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="N57">
+        <v>25315.4</v>
+      </c>
+    </row>
+    <row r="58" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K58" s="2">
+        <v>7723</v>
+      </c>
+      <c r="L58">
+        <f>K58/26.2598</f>
+        <v>294.09972657826796</v>
+      </c>
+      <c r="N58">
+        <v>21934</v>
+      </c>
+    </row>
+    <row r="59" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="N59">
+        <v>149100.65359500001</v>
+      </c>
+    </row>
+    <row r="60" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="N60">
+        <v>78475</v>
+      </c>
+    </row>
+    <row r="61" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="N61">
+        <v>98782.28</v>
+      </c>
+    </row>
+    <row r="62" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="N62">
+        <v>8836.83</v>
+      </c>
+    </row>
+    <row r="63" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="N63">
+        <v>78333.224138000005</v>
+      </c>
+    </row>
+    <row r="64" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="N64">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="65" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N65">
+        <v>13650</v>
+      </c>
+    </row>
+    <row r="66" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N66">
+        <v>5853</v>
+      </c>
+    </row>
+    <row r="67" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N67">
+        <v>19827.428571</v>
+      </c>
+    </row>
+    <row r="68" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N68">
+        <v>8058.9989999999998</v>
+      </c>
+    </row>
+    <row r="69" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N69">
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="70" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N72">
+        <v>5040</v>
+      </c>
+    </row>
+    <row r="73" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N73">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="74" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N74">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="75" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N75">
+        <v>2820</v>
+      </c>
+    </row>
+    <row r="76" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N77">
+        <v>4743.6660000000002</v>
+      </c>
+    </row>
+    <row r="78" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N80">
+        <v>7125</v>
+      </c>
+    </row>
+    <row r="81" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N82">
+        <v>81579.12</v>
+      </c>
+    </row>
+    <row r="83" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N83">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="84" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N84">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="85" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N85">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="86" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N86">
+        <v>139.13999999999999</v>
+      </c>
+    </row>
+    <row r="87" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N87">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N88">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="89" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N89">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="90" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N100">
+        <v>2640</v>
+      </c>
+    </row>
+    <row r="101" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N110">
+        <v>36630</v>
+      </c>
+    </row>
+    <row r="111" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N111">
+        <v>7560</v>
+      </c>
+    </row>
+    <row r="112" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N112">
+        <v>8550</v>
+      </c>
+    </row>
+    <row r="113" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N113" s="6">
+        <f>SUM(N55:N112)</f>
+        <v>899850.74130399991</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -917,4 +1659,2855 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A3E3F36-FCD2-4D59-81CE-AA1D1D1D0627}">
+  <dimension ref="A1:L30"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B1">
+        <v>0</v>
+      </c>
+      <c r="C1">
+        <v>0</v>
+      </c>
+      <c r="D1">
+        <f>B1*C1</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B2">
+        <v>22</v>
+      </c>
+      <c r="C2">
+        <v>821.74</v>
+      </c>
+      <c r="D2">
+        <f>B2*C2</f>
+        <v>18078.28</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>807.04</v>
+      </c>
+      <c r="H2">
+        <f>G2*F2</f>
+        <v>1614.08</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B3">
+        <v>100</v>
+      </c>
+      <c r="C3">
+        <v>807.04</v>
+      </c>
+      <c r="D3">
+        <f t="shared" ref="D3:D4" si="0">B3*C3</f>
+        <v>80704</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>900</v>
+      </c>
+      <c r="H3">
+        <f>G3*F3</f>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>900</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="0"/>
+        <v>4500</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>900</v>
+      </c>
+      <c r="H4">
+        <f>G4*F4</f>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B5" s="7">
+        <f>SUM(B1:B4)</f>
+        <v>127</v>
+      </c>
+      <c r="C5" s="7">
+        <f>SUM(C1:C4)</f>
+        <v>2528.7799999999997</v>
+      </c>
+      <c r="D5" s="7">
+        <f>SUM(D1:D4)</f>
+        <v>103282.28</v>
+      </c>
+      <c r="F5" s="7">
+        <f>SUM(F2:F4)</f>
+        <v>4</v>
+      </c>
+      <c r="G5" s="7">
+        <f>SUM(G2:G4)</f>
+        <v>2607.04</v>
+      </c>
+      <c r="H5" s="8">
+        <f>SUM(H2:H4)</f>
+        <v>3414.08</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="C6" s="9"/>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="D7" s="9">
+        <f>D5/B5</f>
+        <v>813.24629921259839</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <f>B5-F5</f>
+        <v>123</v>
+      </c>
+      <c r="D9" s="9">
+        <f>D5-H5</f>
+        <v>99868.2</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="D11" s="9">
+        <f>D9/B9</f>
+        <v>811.9365853658536</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B14" s="17">
+        <v>1110104</v>
+      </c>
+      <c r="F14">
+        <v>1110201</v>
+      </c>
+      <c r="J14" s="6"/>
+      <c r="L14" s="6">
+        <v>1128432.67</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="6">
+        <v>118382.2</v>
+      </c>
+      <c r="D15" s="6">
+        <v>171047.49</v>
+      </c>
+      <c r="F15" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15" s="6">
+        <v>8350</v>
+      </c>
+      <c r="H15" s="6">
+        <v>100</v>
+      </c>
+      <c r="L15" s="6">
+        <f>C17+G17</f>
+        <v>1165892.92</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="6">
+        <v>1328590.4099999999</v>
+      </c>
+      <c r="D16" s="6">
+        <v>171047.49</v>
+      </c>
+      <c r="F16">
+        <v>8450</v>
+      </c>
+      <c r="G16" s="6">
+        <v>8450</v>
+      </c>
+      <c r="H16" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B17" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="12">
+        <v>1157542.92</v>
+      </c>
+      <c r="D17" s="12"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="G17" s="12">
+        <v>8350</v>
+      </c>
+      <c r="H17" s="12"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="G18" s="16">
+        <v>-7500</v>
+      </c>
+      <c r="J18" s="9"/>
+      <c r="K18" s="13"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="K19" s="6"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="9"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D22" s="6"/>
+      <c r="E22" s="2"/>
+      <c r="H22" s="13"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G23" s="2"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F25" s="6"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="6"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F30" s="9"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BA96DCF-5607-4643-8615-E51DE316F486}">
+  <dimension ref="A1:J162"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>310000085</v>
+      </c>
+      <c r="B1">
+        <v>12</v>
+      </c>
+      <c r="C1">
+        <v>950</v>
+      </c>
+      <c r="D1">
+        <f>B1*C1</f>
+        <v>11400</v>
+      </c>
+      <c r="G1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>310000084</v>
+      </c>
+      <c r="B2">
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <v>1260</v>
+      </c>
+      <c r="D2">
+        <f t="shared" ref="D2:D65" si="0">B2*C2</f>
+        <v>7560</v>
+      </c>
+      <c r="G2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>950</v>
+      </c>
+      <c r="J2">
+        <f>H2*I2</f>
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>310000083</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>12210</v>
+      </c>
+      <c r="D3">
+        <f t="shared" si="0"/>
+        <v>36630</v>
+      </c>
+      <c r="G3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H3">
+        <v>20</v>
+      </c>
+      <c r="I3">
+        <v>200</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J50" si="1">H3*I3</f>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>310000082</v>
+      </c>
+      <c r="B4">
+        <v>20</v>
+      </c>
+      <c r="C4">
+        <v>200</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="0"/>
+        <v>4000</v>
+      </c>
+      <c r="G4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H4">
+        <v>17</v>
+      </c>
+      <c r="I4">
+        <v>123</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="1"/>
+        <v>2091</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>310000081</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>17</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G5" t="s">
+        <v>75</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>3300</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="1"/>
+        <v>9900</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>310000081</v>
+      </c>
+      <c r="B6">
+        <v>17</v>
+      </c>
+      <c r="C6">
+        <v>123</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>2091</v>
+      </c>
+      <c r="G6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>652.1739</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="1"/>
+        <v>652.1739</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>310000080</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>3300</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>9900</v>
+      </c>
+      <c r="G7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H7">
+        <v>59</v>
+      </c>
+      <c r="I7">
+        <v>10</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="1"/>
+        <v>590</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>310000079</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>652.1739</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>652.1739</v>
+      </c>
+      <c r="G8" t="s">
+        <v>78</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>675</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="1"/>
+        <v>675</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>310000078</v>
+      </c>
+      <c r="B9">
+        <v>59</v>
+      </c>
+      <c r="C9">
+        <v>10</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>590</v>
+      </c>
+      <c r="G9" t="s">
+        <v>79</v>
+      </c>
+      <c r="H9">
+        <v>3</v>
+      </c>
+      <c r="I9">
+        <v>1005</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="1"/>
+        <v>3015</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>310000077</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>675</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>675</v>
+      </c>
+      <c r="G10" t="s">
+        <v>80</v>
+      </c>
+      <c r="H10">
+        <v>18</v>
+      </c>
+      <c r="I10">
+        <v>2800</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="1"/>
+        <v>50400</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>310000076</v>
+      </c>
+      <c r="B11">
+        <v>3</v>
+      </c>
+      <c r="C11">
+        <v>1005</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>3015</v>
+      </c>
+      <c r="G11" t="s">
+        <v>81</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>350</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="1"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>310000075</v>
+      </c>
+      <c r="B12">
+        <v>18</v>
+      </c>
+      <c r="C12">
+        <v>2800</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="0"/>
+        <v>50400</v>
+      </c>
+      <c r="G12" t="s">
+        <v>82</v>
+      </c>
+      <c r="H12">
+        <v>10</v>
+      </c>
+      <c r="I12">
+        <v>220</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="1"/>
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>310000071</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>350</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="G13" t="s">
+        <v>83</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>8350</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="1"/>
+        <v>8350</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>310000069</v>
+      </c>
+      <c r="B14">
+        <v>22</v>
+      </c>
+      <c r="C14">
+        <v>220</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="0"/>
+        <v>4840</v>
+      </c>
+      <c r="G14" t="s">
+        <v>84</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>900</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="1"/>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>310000066</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>8350</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="0"/>
+        <v>8350</v>
+      </c>
+      <c r="G15" t="s">
+        <v>85</v>
+      </c>
+      <c r="H15">
+        <v>4</v>
+      </c>
+      <c r="I15">
+        <v>630</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="1"/>
+        <v>2520</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>310000065</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>900</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="0"/>
+        <v>900</v>
+      </c>
+      <c r="G16" t="s">
+        <v>86</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>350</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="1"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>310000059</v>
+      </c>
+      <c r="B17">
+        <v>4</v>
+      </c>
+      <c r="C17">
+        <v>630</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="0"/>
+        <v>2520</v>
+      </c>
+      <c r="G17" t="s">
+        <v>87</v>
+      </c>
+      <c r="H17">
+        <v>3</v>
+      </c>
+      <c r="I17">
+        <v>121.74</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="1"/>
+        <v>365.21999999999997</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>310000058</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>350</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="G18" t="s">
+        <v>88</v>
+      </c>
+      <c r="H18">
+        <v>4</v>
+      </c>
+      <c r="I18">
+        <v>126.09</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="1"/>
+        <v>504.36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>310000056</v>
+      </c>
+      <c r="B19">
+        <v>3</v>
+      </c>
+      <c r="C19">
+        <v>121.74</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="0"/>
+        <v>365.21999999999997</v>
+      </c>
+      <c r="G19" t="s">
+        <v>89</v>
+      </c>
+      <c r="H19">
+        <v>4</v>
+      </c>
+      <c r="I19">
+        <v>108.7</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="1"/>
+        <v>434.8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>310000055</v>
+      </c>
+      <c r="B20">
+        <v>4</v>
+      </c>
+      <c r="C20">
+        <v>126.09</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="0"/>
+        <v>504.36</v>
+      </c>
+      <c r="G20" t="s">
+        <v>89</v>
+      </c>
+      <c r="H20">
+        <v>3</v>
+      </c>
+      <c r="I20">
+        <v>108.69499999999999</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="1"/>
+        <v>326.08499999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>310000054</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>108.7</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="0"/>
+        <v>434.8</v>
+      </c>
+      <c r="G21" t="s">
+        <v>89</v>
+      </c>
+      <c r="H21">
+        <v>3</v>
+      </c>
+      <c r="I21">
+        <v>108.69750000000001</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="1"/>
+        <v>326.09250000000003</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>310000054</v>
+      </c>
+      <c r="B22">
+        <v>3</v>
+      </c>
+      <c r="C22">
+        <v>108.69499999999999</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="0"/>
+        <v>326.08499999999998</v>
+      </c>
+      <c r="G22" t="s">
+        <v>90</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>22.61</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="1"/>
+        <v>22.61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>310000054</v>
+      </c>
+      <c r="B23">
+        <v>3</v>
+      </c>
+      <c r="C23">
+        <v>108.69750000000001</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="0"/>
+        <v>326.09250000000003</v>
+      </c>
+      <c r="G23" t="s">
+        <v>91</v>
+      </c>
+      <c r="H23">
+        <v>3</v>
+      </c>
+      <c r="I23">
+        <v>34.78</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="1"/>
+        <v>104.34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>310000053</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>22.61</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="0"/>
+        <v>22.61</v>
+      </c>
+      <c r="G24" t="s">
+        <v>92</v>
+      </c>
+      <c r="H24">
+        <v>3</v>
+      </c>
+      <c r="I24">
+        <v>113.04</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="1"/>
+        <v>339.12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>310000051</v>
+      </c>
+      <c r="B25">
+        <v>3</v>
+      </c>
+      <c r="C25">
+        <v>34.78</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="0"/>
+        <v>104.34</v>
+      </c>
+      <c r="G25" t="s">
+        <v>93</v>
+      </c>
+      <c r="H25">
+        <v>2</v>
+      </c>
+      <c r="I25">
+        <v>750</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="1"/>
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>310000050</v>
+      </c>
+      <c r="B26">
+        <v>3</v>
+      </c>
+      <c r="C26">
+        <v>113.04</v>
+      </c>
+      <c r="D26">
+        <f t="shared" si="0"/>
+        <v>339.12</v>
+      </c>
+      <c r="G26" t="s">
+        <v>94</v>
+      </c>
+      <c r="H26">
+        <v>3</v>
+      </c>
+      <c r="I26">
+        <v>69.569999999999993</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="1"/>
+        <v>208.70999999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>310000045</v>
+      </c>
+      <c r="B27">
+        <v>10</v>
+      </c>
+      <c r="C27">
+        <v>750</v>
+      </c>
+      <c r="D27">
+        <f t="shared" si="0"/>
+        <v>7500</v>
+      </c>
+      <c r="G27" t="s">
+        <v>95</v>
+      </c>
+      <c r="H27">
+        <v>2</v>
+      </c>
+      <c r="I27">
+        <v>832.44</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="1"/>
+        <v>1664.88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>310000044</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28">
+        <v>160</v>
+      </c>
+      <c r="D28">
+        <f t="shared" si="0"/>
+        <v>160</v>
+      </c>
+      <c r="G28" t="s">
+        <v>96</v>
+      </c>
+      <c r="H28">
+        <v>10</v>
+      </c>
+      <c r="I28">
+        <v>10</v>
+      </c>
+      <c r="J28">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>310000043</v>
+      </c>
+      <c r="B29">
+        <v>2</v>
+      </c>
+      <c r="C29">
+        <v>160</v>
+      </c>
+      <c r="D29">
+        <f t="shared" si="0"/>
+        <v>320</v>
+      </c>
+      <c r="G29" t="s">
+        <v>96</v>
+      </c>
+      <c r="H29">
+        <v>10</v>
+      </c>
+      <c r="I29">
+        <v>75</v>
+      </c>
+      <c r="J29">
+        <f t="shared" si="1"/>
+        <v>750</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>310000042</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30">
+        <v>69.569999999999993</v>
+      </c>
+      <c r="D30">
+        <f t="shared" si="0"/>
+        <v>347.84999999999997</v>
+      </c>
+      <c r="G30" t="s">
+        <v>97</v>
+      </c>
+      <c r="H30">
+        <v>5</v>
+      </c>
+      <c r="I30">
+        <v>75</v>
+      </c>
+      <c r="J30">
+        <f t="shared" si="1"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>310000041</v>
+      </c>
+      <c r="B31">
+        <v>6</v>
+      </c>
+      <c r="C31">
+        <v>300</v>
+      </c>
+      <c r="D31">
+        <f t="shared" si="0"/>
+        <v>1800</v>
+      </c>
+      <c r="G31" t="s">
+        <v>98</v>
+      </c>
+      <c r="H31">
+        <v>2</v>
+      </c>
+      <c r="I31">
+        <v>165.22</v>
+      </c>
+      <c r="J31">
+        <f t="shared" si="1"/>
+        <v>330.44</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>310000040</v>
+      </c>
+      <c r="B32">
+        <v>6</v>
+      </c>
+      <c r="C32">
+        <v>140</v>
+      </c>
+      <c r="D32">
+        <f t="shared" si="0"/>
+        <v>840</v>
+      </c>
+      <c r="G32" t="s">
+        <v>99</v>
+      </c>
+      <c r="H32">
+        <v>12</v>
+      </c>
+      <c r="I32">
+        <v>103.083</v>
+      </c>
+      <c r="J32">
+        <f t="shared" si="1"/>
+        <v>1236.9960000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>310000039</v>
+      </c>
+      <c r="B33">
+        <v>14</v>
+      </c>
+      <c r="C33">
+        <v>90</v>
+      </c>
+      <c r="D33">
+        <f t="shared" si="0"/>
+        <v>1260</v>
+      </c>
+      <c r="G33" t="s">
+        <v>100</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="I33">
+        <v>385</v>
+      </c>
+      <c r="J33">
+        <f t="shared" si="1"/>
+        <v>385</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>310000038</v>
+      </c>
+      <c r="B34">
+        <v>100</v>
+      </c>
+      <c r="C34">
+        <v>832.44</v>
+      </c>
+      <c r="D34">
+        <f t="shared" si="0"/>
+        <v>83244</v>
+      </c>
+      <c r="G34" t="s">
+        <v>101</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+      <c r="I34">
+        <v>395</v>
+      </c>
+      <c r="J34">
+        <f t="shared" si="1"/>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>310000036</v>
+      </c>
+      <c r="B35">
+        <v>10</v>
+      </c>
+      <c r="C35">
+        <v>10</v>
+      </c>
+      <c r="D35">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="G35" t="s">
+        <v>102</v>
+      </c>
+      <c r="H35">
+        <v>2</v>
+      </c>
+      <c r="I35">
+        <v>1437</v>
+      </c>
+      <c r="J35">
+        <f t="shared" si="1"/>
+        <v>2874</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>310000036</v>
+      </c>
+      <c r="B36">
+        <v>10</v>
+      </c>
+      <c r="C36">
+        <v>75</v>
+      </c>
+      <c r="D36">
+        <f t="shared" si="0"/>
+        <v>750</v>
+      </c>
+      <c r="G36" t="s">
+        <v>103</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36">
+        <v>1750</v>
+      </c>
+      <c r="J36">
+        <f t="shared" si="1"/>
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>310000035</v>
+      </c>
+      <c r="B37">
+        <v>100</v>
+      </c>
+      <c r="C37">
+        <v>75</v>
+      </c>
+      <c r="D37">
+        <f t="shared" si="0"/>
+        <v>7500</v>
+      </c>
+      <c r="G37" t="s">
+        <v>104</v>
+      </c>
+      <c r="H37">
+        <v>1</v>
+      </c>
+      <c r="I37">
+        <v>3200</v>
+      </c>
+      <c r="J37">
+        <f t="shared" si="1"/>
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>310000033</v>
+      </c>
+      <c r="B38">
+        <v>2</v>
+      </c>
+      <c r="C38">
+        <v>165.22</v>
+      </c>
+      <c r="D38">
+        <f t="shared" si="0"/>
+        <v>330.44</v>
+      </c>
+      <c r="G38" t="s">
+        <v>105</v>
+      </c>
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="I38">
+        <v>3304.5709999999999</v>
+      </c>
+      <c r="J38">
+        <f t="shared" si="1"/>
+        <v>3304.5709999999999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>310000026</v>
+      </c>
+      <c r="B39">
+        <v>12</v>
+      </c>
+      <c r="C39">
+        <v>103.083</v>
+      </c>
+      <c r="D39">
+        <f t="shared" si="0"/>
+        <v>1236.9960000000001</v>
+      </c>
+      <c r="G39" t="s">
+        <v>106</v>
+      </c>
+      <c r="H39">
+        <v>2</v>
+      </c>
+      <c r="I39">
+        <v>1951</v>
+      </c>
+      <c r="J39">
+        <f t="shared" si="1"/>
+        <v>3902</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>310000025</v>
+      </c>
+      <c r="B40">
+        <v>12</v>
+      </c>
+      <c r="C40">
+        <v>340</v>
+      </c>
+      <c r="D40">
+        <f t="shared" si="0"/>
+        <v>4080</v>
+      </c>
+      <c r="G40" t="s">
+        <v>107</v>
+      </c>
+      <c r="H40">
+        <v>3</v>
+      </c>
+      <c r="I40">
+        <v>4550</v>
+      </c>
+      <c r="J40">
+        <f t="shared" si="1"/>
+        <v>13650</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>310000025</v>
+      </c>
+      <c r="B41">
+        <v>2</v>
+      </c>
+      <c r="C41">
+        <v>331.83300000000003</v>
+      </c>
+      <c r="D41">
+        <f t="shared" si="0"/>
+        <v>663.66600000000005</v>
+      </c>
+      <c r="G41" t="s">
+        <v>108</v>
+      </c>
+      <c r="H41">
+        <v>150</v>
+      </c>
+      <c r="I41">
+        <v>160</v>
+      </c>
+      <c r="J41">
+        <f t="shared" si="1"/>
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>310000024</v>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42">
+        <v>385</v>
+      </c>
+      <c r="D42">
+        <f t="shared" si="0"/>
+        <v>385</v>
+      </c>
+      <c r="G42" t="s">
+        <v>109</v>
+      </c>
+      <c r="H42">
+        <v>8</v>
+      </c>
+      <c r="I42">
+        <v>740.42</v>
+      </c>
+      <c r="J42">
+        <f t="shared" si="1"/>
+        <v>5923.36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>310000023</v>
+      </c>
+      <c r="B43">
+        <v>3</v>
+      </c>
+      <c r="C43">
+        <v>304</v>
+      </c>
+      <c r="D43">
+        <f t="shared" si="0"/>
+        <v>912</v>
+      </c>
+      <c r="G43" t="s">
+        <v>109</v>
+      </c>
+      <c r="H43">
+        <v>1</v>
+      </c>
+      <c r="I43">
+        <v>732.08600000000001</v>
+      </c>
+      <c r="J43">
+        <f t="shared" si="1"/>
+        <v>732.08600000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>310000023</v>
+      </c>
+      <c r="B44">
+        <v>6</v>
+      </c>
+      <c r="C44">
+        <v>318</v>
+      </c>
+      <c r="D44">
+        <f t="shared" si="0"/>
+        <v>1908</v>
+      </c>
+      <c r="G44" t="s">
+        <v>110</v>
+      </c>
+      <c r="H44">
+        <v>30</v>
+      </c>
+      <c r="I44">
+        <v>384.21</v>
+      </c>
+      <c r="J44">
+        <f t="shared" si="1"/>
+        <v>11526.3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>310000021</v>
+      </c>
+      <c r="B45">
+        <v>2</v>
+      </c>
+      <c r="C45">
+        <v>630</v>
+      </c>
+      <c r="D45">
+        <f t="shared" si="0"/>
+        <v>1260</v>
+      </c>
+      <c r="G45" t="s">
+        <v>111</v>
+      </c>
+      <c r="H45">
+        <v>10</v>
+      </c>
+      <c r="I45">
+        <v>1075</v>
+      </c>
+      <c r="J45">
+        <f t="shared" si="1"/>
+        <v>10750</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>310000020</v>
+      </c>
+      <c r="B46">
+        <v>2</v>
+      </c>
+      <c r="C46">
+        <v>395</v>
+      </c>
+      <c r="D46">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="G46" t="s">
+        <v>112</v>
+      </c>
+      <c r="H46">
+        <v>245</v>
+      </c>
+      <c r="I46">
+        <v>695</v>
+      </c>
+      <c r="J46">
+        <f t="shared" si="1"/>
+        <v>170275</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>310000019</v>
+      </c>
+      <c r="B47">
+        <v>9</v>
+      </c>
+      <c r="C47">
+        <v>560</v>
+      </c>
+      <c r="D47">
+        <f t="shared" si="0"/>
+        <v>5040</v>
+      </c>
+      <c r="G47" t="s">
+        <v>113</v>
+      </c>
+      <c r="H47">
+        <v>25</v>
+      </c>
+      <c r="I47">
+        <v>997</v>
+      </c>
+      <c r="J47">
+        <f t="shared" si="1"/>
+        <v>24925</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>310000018</v>
+      </c>
+      <c r="B48">
+        <v>2</v>
+      </c>
+      <c r="C48">
+        <v>1437</v>
+      </c>
+      <c r="D48">
+        <f t="shared" si="0"/>
+        <v>2874</v>
+      </c>
+      <c r="G48" t="s">
+        <v>114</v>
+      </c>
+      <c r="H48">
+        <v>58</v>
+      </c>
+      <c r="I48">
+        <v>684.2</v>
+      </c>
+      <c r="J48">
+        <f t="shared" si="1"/>
+        <v>39683.600000000006</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>310000017</v>
+      </c>
+      <c r="B49">
+        <v>1</v>
+      </c>
+      <c r="C49">
+        <v>1750</v>
+      </c>
+      <c r="D49">
+        <f t="shared" si="0"/>
+        <v>1750</v>
+      </c>
+      <c r="G49" t="s">
+        <v>115</v>
+      </c>
+      <c r="H49">
+        <v>26</v>
+      </c>
+      <c r="I49">
+        <v>597</v>
+      </c>
+      <c r="J49">
+        <f t="shared" si="1"/>
+        <v>15522</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>310000016</v>
+      </c>
+      <c r="B50">
+        <v>3</v>
+      </c>
+      <c r="C50">
+        <v>3200</v>
+      </c>
+      <c r="D50">
+        <f t="shared" si="0"/>
+        <v>9600</v>
+      </c>
+      <c r="G50" t="s">
+        <v>116</v>
+      </c>
+      <c r="H50">
+        <v>77</v>
+      </c>
+      <c r="I50">
+        <v>615</v>
+      </c>
+      <c r="J50">
+        <f t="shared" si="1"/>
+        <v>47355</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>310000015</v>
+      </c>
+      <c r="B51">
+        <v>3</v>
+      </c>
+      <c r="C51">
+        <v>2686.3330000000001</v>
+      </c>
+      <c r="D51">
+        <f t="shared" si="0"/>
+        <v>8058.9989999999998</v>
+      </c>
+      <c r="J51" s="6">
+        <f>SUM(J2:J50)</f>
+        <v>477584.74439999997</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>310000014</v>
+      </c>
+      <c r="B52">
+        <v>1</v>
+      </c>
+      <c r="C52">
+        <v>3200</v>
+      </c>
+      <c r="D52">
+        <f t="shared" si="0"/>
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>310000014</v>
+      </c>
+      <c r="B53">
+        <v>6</v>
+      </c>
+      <c r="C53">
+        <v>3322</v>
+      </c>
+      <c r="D53">
+        <f t="shared" si="0"/>
+        <v>19932</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>310000013</v>
+      </c>
+      <c r="B54">
+        <v>5</v>
+      </c>
+      <c r="C54">
+        <v>1951</v>
+      </c>
+      <c r="D54">
+        <f t="shared" si="0"/>
+        <v>9755</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>310000012</v>
+      </c>
+      <c r="B55">
+        <v>6</v>
+      </c>
+      <c r="C55">
+        <v>4550</v>
+      </c>
+      <c r="D55">
+        <f t="shared" si="0"/>
+        <v>27300</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>310000011</v>
+      </c>
+      <c r="B56">
+        <v>200</v>
+      </c>
+      <c r="C56">
+        <v>160</v>
+      </c>
+      <c r="D56">
+        <f t="shared" si="0"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>310000010</v>
+      </c>
+      <c r="B57">
+        <v>16</v>
+      </c>
+      <c r="C57">
+        <v>680</v>
+      </c>
+      <c r="D57">
+        <f t="shared" si="0"/>
+        <v>10880</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>310000010</v>
+      </c>
+      <c r="B58">
+        <v>100</v>
+      </c>
+      <c r="C58">
+        <v>740.42</v>
+      </c>
+      <c r="D58">
+        <f t="shared" si="0"/>
+        <v>74042</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>310000009</v>
+      </c>
+      <c r="B59">
+        <v>53</v>
+      </c>
+      <c r="C59">
+        <v>384.21</v>
+      </c>
+      <c r="D59">
+        <f t="shared" si="0"/>
+        <v>20363.129999999997</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>310000007</v>
+      </c>
+      <c r="B60">
+        <v>100</v>
+      </c>
+      <c r="C60">
+        <v>807.04</v>
+      </c>
+      <c r="D60">
+        <f t="shared" si="0"/>
+        <v>80704</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>310000007</v>
+      </c>
+      <c r="B61">
+        <v>22</v>
+      </c>
+      <c r="C61">
+        <v>821.74</v>
+      </c>
+      <c r="D61">
+        <f t="shared" si="0"/>
+        <v>18078.28</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>310000006</v>
+      </c>
+      <c r="B62">
+        <v>83</v>
+      </c>
+      <c r="C62">
+        <v>1075</v>
+      </c>
+      <c r="D62">
+        <f t="shared" si="0"/>
+        <v>89225</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>310000005</v>
+      </c>
+      <c r="B63">
+        <v>159</v>
+      </c>
+      <c r="C63">
+        <v>700</v>
+      </c>
+      <c r="D63">
+        <f t="shared" si="0"/>
+        <v>111300</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>310000005</v>
+      </c>
+      <c r="B64">
+        <v>300</v>
+      </c>
+      <c r="C64">
+        <v>695</v>
+      </c>
+      <c r="D64">
+        <f t="shared" si="0"/>
+        <v>208500</v>
+      </c>
+      <c r="I64" s="9">
+        <f>D69-J51</f>
+        <v>900208.41800000006</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>310000004</v>
+      </c>
+      <c r="B65">
+        <v>47</v>
+      </c>
+      <c r="C65">
+        <v>997</v>
+      </c>
+      <c r="D65">
+        <f t="shared" si="0"/>
+        <v>46859</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>310000003</v>
+      </c>
+      <c r="B66">
+        <v>95</v>
+      </c>
+      <c r="C66">
+        <v>684.2</v>
+      </c>
+      <c r="D66">
+        <f t="shared" ref="D66:D68" si="2">B66*C66</f>
+        <v>64999.000000000007</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>310000002</v>
+      </c>
+      <c r="B67">
+        <v>132</v>
+      </c>
+      <c r="C67">
+        <v>597</v>
+      </c>
+      <c r="D67">
+        <f t="shared" si="2"/>
+        <v>78804</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>310000001</v>
+      </c>
+      <c r="B68">
+        <v>313</v>
+      </c>
+      <c r="C68">
+        <v>615</v>
+      </c>
+      <c r="D68">
+        <f t="shared" si="2"/>
+        <v>192495</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D69" s="6">
+        <f>SUM(D1:D68)</f>
+        <v>1377793.1624</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H72">
+        <v>-3300</v>
+      </c>
+      <c r="J72">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B73" s="6"/>
+      <c r="H73">
+        <v>-2091</v>
+      </c>
+      <c r="J73">
+        <v>22.61</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H74">
+        <v>20</v>
+      </c>
+      <c r="J74">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H75">
+        <v>22.61</v>
+      </c>
+      <c r="J75">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H76">
+        <v>100</v>
+      </c>
+      <c r="J76">
+        <v>104.34</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H77">
+        <v>100</v>
+      </c>
+      <c r="J77">
+        <v>121.74</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H78">
+        <v>104.34</v>
+      </c>
+      <c r="J78">
+        <v>121.74</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H79">
+        <v>121.74</v>
+      </c>
+      <c r="J79">
+        <v>121.74</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H80">
+        <v>121.74</v>
+      </c>
+      <c r="J80">
+        <v>126.09</v>
+      </c>
+    </row>
+    <row r="81" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H81">
+        <v>121.74</v>
+      </c>
+      <c r="J81">
+        <v>126.09</v>
+      </c>
+    </row>
+    <row r="82" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H82">
+        <v>126.09</v>
+      </c>
+      <c r="J82">
+        <v>126.09</v>
+      </c>
+    </row>
+    <row r="83" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H83">
+        <v>126.09</v>
+      </c>
+      <c r="J83">
+        <v>126.09</v>
+      </c>
+    </row>
+    <row r="84" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H84">
+        <v>126.09</v>
+      </c>
+      <c r="J84">
+        <v>165.22</v>
+      </c>
+    </row>
+    <row r="85" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H85">
+        <v>126.09</v>
+      </c>
+      <c r="J85">
+        <v>165.22</v>
+      </c>
+    </row>
+    <row r="86" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H86">
+        <v>139.13999999999999</v>
+      </c>
+      <c r="J86">
+        <v>208.71</v>
+      </c>
+    </row>
+    <row r="87" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H87">
+        <v>160</v>
+      </c>
+      <c r="J87">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="88" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H88">
+        <v>165.22</v>
+      </c>
+      <c r="J88">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="89" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H89">
+        <v>165.22</v>
+      </c>
+      <c r="J89">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="90" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H90">
+        <v>208.71</v>
+      </c>
+      <c r="J90">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="91" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H91">
+        <v>220</v>
+      </c>
+      <c r="J91">
+        <v>326.08499999999998</v>
+      </c>
+    </row>
+    <row r="92" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H92">
+        <v>220</v>
+      </c>
+      <c r="J92">
+        <v>326.09249999999997</v>
+      </c>
+    </row>
+    <row r="93" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H93">
+        <v>320</v>
+      </c>
+      <c r="J93">
+        <v>339.12</v>
+      </c>
+    </row>
+    <row r="94" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H94">
+        <v>326.08499999999998</v>
+      </c>
+      <c r="J94">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="95" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H95">
+        <v>326.09249999999997</v>
+      </c>
+      <c r="J95">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="96" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H96">
+        <v>339.12</v>
+      </c>
+      <c r="J96">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="97" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H97">
+        <v>350</v>
+      </c>
+      <c r="J97">
+        <v>384.21</v>
+      </c>
+    </row>
+    <row r="98" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H98">
+        <v>350</v>
+      </c>
+      <c r="J98">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="99" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H99">
+        <v>385</v>
+      </c>
+      <c r="J99">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="100" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H100">
+        <v>434.8</v>
+      </c>
+      <c r="J100">
+        <v>434.8</v>
+      </c>
+    </row>
+    <row r="101" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H101">
+        <v>440</v>
+      </c>
+      <c r="J101">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="102" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H102">
+        <v>440</v>
+      </c>
+      <c r="J102">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="103" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H103">
+        <v>470</v>
+      </c>
+      <c r="J103">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="104" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H104">
+        <v>630</v>
+      </c>
+      <c r="J104">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="105" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H105">
+        <v>630</v>
+      </c>
+      <c r="J105">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="106" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H106">
+        <v>652.1739</v>
+      </c>
+      <c r="J106">
+        <v>652.1739</v>
+      </c>
+    </row>
+    <row r="107" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H107">
+        <v>663.66600000000005</v>
+      </c>
+      <c r="J107">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="108" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H108">
+        <v>675</v>
+      </c>
+      <c r="J108">
+        <v>684.2</v>
+      </c>
+    </row>
+    <row r="109" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H109">
+        <v>750</v>
+      </c>
+      <c r="J109">
+        <v>732.08600000000001</v>
+      </c>
+    </row>
+    <row r="110" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H110">
+        <v>790</v>
+      </c>
+      <c r="J110">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="111" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H111">
+        <v>840</v>
+      </c>
+      <c r="J111">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="112" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H112">
+        <v>880</v>
+      </c>
+      <c r="J112">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="113" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H113">
+        <v>900</v>
+      </c>
+      <c r="J113">
+        <v>832.44</v>
+      </c>
+    </row>
+    <row r="114" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H114">
+        <v>912</v>
+      </c>
+      <c r="J114">
+        <v>832.44</v>
+      </c>
+    </row>
+    <row r="115" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H115">
+        <v>1236.9960000000001</v>
+      </c>
+      <c r="J115">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="116" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H116">
+        <v>1260</v>
+      </c>
+      <c r="J116">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="117" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H117">
+        <v>1260</v>
+      </c>
+      <c r="J117">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="118" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H118">
+        <v>1260</v>
+      </c>
+      <c r="J118">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="119" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H119">
+        <v>1750</v>
+      </c>
+      <c r="J119">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="120" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H120">
+        <v>1800</v>
+      </c>
+      <c r="J120">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="121" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H121">
+        <v>1908</v>
+      </c>
+      <c r="J121">
+        <v>1236.9960000000001</v>
+      </c>
+    </row>
+    <row r="122" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H122">
+        <v>2091</v>
+      </c>
+      <c r="J122">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="123" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H123">
+        <v>2091</v>
+      </c>
+      <c r="J123">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="124" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H124">
+        <v>2640</v>
+      </c>
+      <c r="J124">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="125" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H125">
+        <v>2874</v>
+      </c>
+      <c r="J125">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="126" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H126">
+        <v>3015</v>
+      </c>
+      <c r="J126">
+        <v>1921.05</v>
+      </c>
+    </row>
+    <row r="127" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H127">
+        <v>3200</v>
+      </c>
+      <c r="J127">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="128" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H128">
+        <v>3300</v>
+      </c>
+      <c r="J128">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="129" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H129">
+        <v>3300</v>
+      </c>
+      <c r="J129">
+        <v>2091</v>
+      </c>
+    </row>
+    <row r="130" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H130">
+        <v>4000</v>
+      </c>
+      <c r="J130">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="131" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H131">
+        <v>4080</v>
+      </c>
+      <c r="J131">
+        <v>2991</v>
+      </c>
+    </row>
+    <row r="132" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H132">
+        <v>4550</v>
+      </c>
+      <c r="J132">
+        <v>3015</v>
+      </c>
+    </row>
+    <row r="133" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H133">
+        <v>5040</v>
+      </c>
+      <c r="J133">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="134" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H134">
+        <v>6600</v>
+      </c>
+      <c r="J134">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="135" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H135">
+        <v>7500</v>
+      </c>
+      <c r="J135">
+        <v>3304.5709999999999</v>
+      </c>
+    </row>
+    <row r="136" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H136">
+        <v>7500</v>
+      </c>
+      <c r="J136">
+        <v>3582</v>
+      </c>
+    </row>
+    <row r="137" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H137">
+        <v>7560</v>
+      </c>
+      <c r="J137">
+        <v>3690</v>
+      </c>
+    </row>
+    <row r="138" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H138">
+        <v>8058.9989999999998</v>
+      </c>
+      <c r="J138">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="139" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H139">
+        <v>8350</v>
+      </c>
+      <c r="J139">
+        <v>4550</v>
+      </c>
+    </row>
+    <row r="140" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H140">
+        <v>9600</v>
+      </c>
+      <c r="J140">
+        <v>4789.3999999999996</v>
+      </c>
+    </row>
+    <row r="141" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H141">
+        <v>9755</v>
+      </c>
+      <c r="J141">
+        <v>4985</v>
+      </c>
+    </row>
+    <row r="142" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H142">
+        <v>10880</v>
+      </c>
+      <c r="J142">
+        <v>5923.36</v>
+      </c>
+    </row>
+    <row r="143" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H143">
+        <v>11400</v>
+      </c>
+      <c r="J143">
+        <v>5982</v>
+      </c>
+    </row>
+    <row r="144" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H144">
+        <v>18078.28</v>
+      </c>
+      <c r="J144">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>119</v>
+      </c>
+      <c r="B145" t="s">
+        <v>120</v>
+      </c>
+      <c r="C145" t="s">
+        <v>121</v>
+      </c>
+      <c r="D145" t="s">
+        <v>122</v>
+      </c>
+      <c r="E145" t="s">
+        <v>123</v>
+      </c>
+      <c r="H145">
+        <v>19932</v>
+      </c>
+      <c r="J145">
+        <v>6979</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>112</v>
+      </c>
+      <c r="B146" t="s">
+        <v>124</v>
+      </c>
+      <c r="C146" t="s">
+        <v>125</v>
+      </c>
+      <c r="D146">
+        <v>300</v>
+      </c>
+      <c r="E146">
+        <v>695</v>
+      </c>
+      <c r="F146">
+        <f>D146*E146</f>
+        <v>208500</v>
+      </c>
+      <c r="H146">
+        <v>20363.13</v>
+      </c>
+      <c r="J146">
+        <v>8350</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>112</v>
+      </c>
+      <c r="B147" t="s">
+        <v>124</v>
+      </c>
+      <c r="C147" t="s">
+        <v>125</v>
+      </c>
+      <c r="D147">
+        <v>159</v>
+      </c>
+      <c r="E147">
+        <v>700</v>
+      </c>
+      <c r="F147">
+        <f>D147*E147</f>
+        <v>111300</v>
+      </c>
+      <c r="G147">
+        <f>(F146+F147)/(D146+D147)</f>
+        <v>696.7320261437909</v>
+      </c>
+      <c r="H147">
+        <v>22750</v>
+      </c>
+      <c r="J147">
+        <v>9100</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>112</v>
+      </c>
+      <c r="B148" t="s">
+        <v>126</v>
+      </c>
+      <c r="C148" t="s">
+        <v>127</v>
+      </c>
+      <c r="D148">
+        <v>18</v>
+      </c>
+      <c r="E148">
+        <v>695</v>
+      </c>
+      <c r="F148" s="6">
+        <f>SUM(F146:F147)</f>
+        <v>319800</v>
+      </c>
+      <c r="G148" s="6">
+        <f>(D146+D147)*G147</f>
+        <v>319800</v>
+      </c>
+      <c r="H148">
+        <v>32000</v>
+      </c>
+      <c r="J148">
+        <v>9221.0400000000009</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>112</v>
+      </c>
+      <c r="B149" t="s">
+        <v>128</v>
+      </c>
+      <c r="C149" t="s">
+        <v>127</v>
+      </c>
+      <c r="D149">
+        <v>32</v>
+      </c>
+      <c r="E149">
+        <v>695</v>
+      </c>
+      <c r="H149">
+        <v>36630</v>
+      </c>
+      <c r="J149">
+        <v>10750</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>112</v>
+      </c>
+      <c r="B150" t="s">
+        <v>129</v>
+      </c>
+      <c r="C150" t="s">
+        <v>127</v>
+      </c>
+      <c r="D150">
+        <v>40</v>
+      </c>
+      <c r="E150">
+        <v>695</v>
+      </c>
+      <c r="H150">
+        <v>46859</v>
+      </c>
+      <c r="J150">
+        <v>11940</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>112</v>
+      </c>
+      <c r="B151" t="s">
+        <v>130</v>
+      </c>
+      <c r="C151" t="s">
+        <v>127</v>
+      </c>
+      <c r="D151">
+        <v>25</v>
+      </c>
+      <c r="E151">
+        <v>695</v>
+      </c>
+      <c r="H151">
+        <v>50400</v>
+      </c>
+      <c r="J151">
+        <v>12300</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>112</v>
+      </c>
+      <c r="B152" t="s">
+        <v>131</v>
+      </c>
+      <c r="C152" t="s">
+        <v>127</v>
+      </c>
+      <c r="D152">
+        <v>30</v>
+      </c>
+      <c r="E152">
+        <v>695</v>
+      </c>
+      <c r="H152">
+        <v>64999</v>
+      </c>
+      <c r="J152">
+        <v>12510</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>112</v>
+      </c>
+      <c r="B153" t="s">
+        <v>132</v>
+      </c>
+      <c r="C153" t="s">
+        <v>127</v>
+      </c>
+      <c r="D153">
+        <v>100</v>
+      </c>
+      <c r="E153">
+        <v>695</v>
+      </c>
+      <c r="H153">
+        <v>74042</v>
+      </c>
+      <c r="J153">
+        <v>17375</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D154">
+        <f>SUM(D146:D153)</f>
+        <v>704</v>
+      </c>
+      <c r="H154">
+        <v>78804</v>
+      </c>
+      <c r="J154">
+        <v>20850</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H155">
+        <v>80704</v>
+      </c>
+      <c r="J155">
+        <v>22240</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H156">
+        <v>83244</v>
+      </c>
+      <c r="J156">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H157">
+        <v>89225</v>
+      </c>
+      <c r="J157">
+        <v>27800</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H158">
+        <v>111300</v>
+      </c>
+      <c r="J158">
+        <v>30750</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H159">
+        <v>192495</v>
+      </c>
+      <c r="J159">
+        <v>34210</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H160">
+        <v>208500</v>
+      </c>
+      <c r="J160">
+        <v>50400</v>
+      </c>
+    </row>
+    <row r="161" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H161" s="8">
+        <f>SUM(H72:H160)</f>
+        <v>1377793.1624</v>
+      </c>
+      <c r="J161">
+        <v>69500</v>
+      </c>
+    </row>
+    <row r="162" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="J162" s="6">
+        <f>SUM(J72:J161)</f>
+        <v>477584.74439999997</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/textos/CONTROL DE CAMBIOS APARTIR DE LA 6.3.1.xlsx
+++ b/textos/CONTROL DE CAMBIOS APARTIR DE LA 6.3.1.xlsx
@@ -1,22 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\HOME OFFICE\ERP- COMEGCEN - SEMUBI - FLOR\ERP - SISC\ERP\textos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C0A580-48CC-4C24-945E-BF1CF5BD5D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11918F68-7602-441C-BA1F-A2B4B3F3994B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="CAMBIOS" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
-    <sheet name="Hoja3" sheetId="3" r:id="rId3"/>
+    <sheet name="CASOS ERP" sheetId="4" r:id="rId1"/>
+    <sheet name="CAMBIOS" sheetId="1" r:id="rId2"/>
+    <sheet name="Hoja2" sheetId="2" r:id="rId3"/>
+    <sheet name="Hoja3" sheetId="3" r:id="rId4"/>
+    <sheet name="Hoja4" sheetId="5" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Hoja4!$A$1:$H$413</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="184">
   <si>
     <t xml:space="preserve">CONTRO DE CAMBIOS DE ERP SISC </t>
   </si>
@@ -453,6 +458,141 @@
   </si>
   <si>
     <t>nuevo reporte de existencias por fehca</t>
+  </si>
+  <si>
+    <t>W_Select_Rep_I</t>
+  </si>
+  <si>
+    <t>mejoras al kardex por producto</t>
+  </si>
+  <si>
+    <t>FILTROS Y DATA AUTOMATICA</t>
+  </si>
+  <si>
+    <t>AGREGADO CAMPO CXV_CLI_COD</t>
+  </si>
+  <si>
+    <t>FILES COBROS_X_VALES</t>
+  </si>
+  <si>
+    <t>para traer saldo de vales corretos</t>
+  </si>
+  <si>
+    <t>w_cobro_vales</t>
+  </si>
+  <si>
+    <t>modificaciuon meotodos crud de vales enb salidas</t>
+  </si>
+  <si>
+    <t>se creo script para acttulizacar el nuevo campo</t>
+  </si>
+  <si>
+    <t>w_bod_detall_s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">se adapto el </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rutina - 15 septiembre </t>
+  </si>
+  <si>
+    <t>completo</t>
+  </si>
+  <si>
+    <t>Fallo en generacion de reporte final</t>
+  </si>
+  <si>
+    <t>14035 - Reincidencia decimales en reportes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">completo </t>
+  </si>
+  <si>
+    <t>se agregaron campos a las tablas de cxv, identificacion de cliente</t>
+  </si>
+  <si>
+    <t>13196 - Descuadre en reporte Vrs. Saldos Cuentas por Cobrar</t>
+  </si>
+  <si>
+    <t>en desarrollo</t>
+  </si>
+  <si>
+    <t>creacion de rutina e identificacion de facturas con vales sin pagos</t>
+  </si>
+  <si>
+    <t>12631 - Ajustes de inventario</t>
+  </si>
+  <si>
+    <t>en desarrollo / por validar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">se ajsuto el reporte a costo promedio, aun no cuadra la cuenta designada con las existencias a la fecha (por sitemas heredado de version inicial de erp) o por ajustes manuales </t>
+  </si>
+  <si>
+    <t>14670 - ERROR EN REPORTES ERP CASO RAFAGA LITRO</t>
+  </si>
+  <si>
+    <t>---</t>
+  </si>
+  <si>
+    <t>mismo que el caso 14494</t>
+  </si>
+  <si>
+    <t>14494 - KARDEX POR PRODUCTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">en desarrollo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">se esta trabajando en una version general. La trabajada hasta ahora solo se puede acceder por determinado producto, cuadrar salidas y arregalar filtros </t>
+  </si>
+  <si>
+    <t>14364 - CORRECCION LIBRO DE VENTAS Y COMPRAS</t>
+  </si>
+  <si>
+    <t>se arreglo los totales calculos de impuestos y exentos esmugrupal</t>
+  </si>
+  <si>
+    <t>completo / por validar comegecen</t>
+  </si>
+  <si>
+    <t>14184 - puntos varios ERP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">para esmugrupal esta correcto, definir fallas en comegcen </t>
+  </si>
+  <si>
+    <t>Definicion</t>
+  </si>
+  <si>
+    <t>Estado actual</t>
+  </si>
+  <si>
+    <t>Observaciones</t>
+  </si>
+  <si>
+    <t>✔️</t>
+  </si>
+  <si>
+    <t>14714 - Reincidencia Vales en Negativo</t>
+  </si>
+  <si>
+    <t>Semana 04-05-2026</t>
+  </si>
+  <si>
+    <t>u</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>sub</t>
+  </si>
+  <si>
+    <t>M_Rep_CXC</t>
+  </si>
+  <si>
+    <t>se interpolo los vales en el reporte para que cuadren saldos</t>
   </si>
 </sst>
 </file>
@@ -545,7 +685,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -564,14 +704,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
@@ -853,6 +995,162 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50EBBD9B-B973-419E-B723-706D7A196B5A}">
+  <dimension ref="A3:F23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="61.44140625" customWidth="1"/>
+    <col min="2" max="2" width="38.33203125" customWidth="1"/>
+    <col min="3" max="3" width="59" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>153</v>
+      </c>
+      <c r="B5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>177</v>
+      </c>
+      <c r="B6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D6" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>156</v>
+      </c>
+      <c r="B7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>159</v>
+      </c>
+      <c r="B8" t="s">
+        <v>160</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>162</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>165</v>
+      </c>
+      <c r="B10" t="s">
+        <v>166</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D10" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>168</v>
+      </c>
+      <c r="B11" t="s">
+        <v>170</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D11" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>171</v>
+      </c>
+      <c r="B12" t="s">
+        <v>166</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D12" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="23" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F23" s="2">
+        <v>1248848.4099999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P113"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -861,102 +1159,102 @@
     <col min="3" max="3" width="48.33203125" customWidth="1"/>
     <col min="4" max="4" width="39.33203125" customWidth="1"/>
     <col min="5" max="5" width="10.33203125" customWidth="1"/>
-    <col min="6" max="6" width="22.21875" customWidth="1"/>
+    <col min="6" max="6" width="22.33203125" customWidth="1"/>
     <col min="8" max="8" width="13.109375" customWidth="1"/>
-    <col min="14" max="14" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="14"/>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="14"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="18"/>
+      <c r="M5" s="18"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
@@ -1306,7 +1604,7 @@
       </c>
     </row>
     <row r="35" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="14" t="s">
         <v>136</v>
       </c>
       <c r="D35" t="s">
@@ -1341,317 +1639,65 @@
         <v>47</v>
       </c>
     </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C37" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D37" t="s">
+        <v>139</v>
+      </c>
+      <c r="E37" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="38" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C38" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D38" t="s">
+        <v>143</v>
+      </c>
+      <c r="E38" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C39" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D39" t="s">
+        <v>145</v>
+      </c>
+    </row>
     <row r="40" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D40" s="2"/>
+      <c r="C40" s="5" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="41" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D41" s="2"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D42" s="2"/>
-    </row>
-    <row r="55" spans="11:14" x14ac:dyDescent="0.3">
-      <c r="N55">
-        <v>145140</v>
-      </c>
-    </row>
-    <row r="56" spans="11:14" x14ac:dyDescent="0.3">
-      <c r="N56">
-        <v>63282</v>
-      </c>
-    </row>
-    <row r="57" spans="11:14" x14ac:dyDescent="0.3">
-      <c r="N57">
-        <v>25315.4</v>
-      </c>
-    </row>
-    <row r="58" spans="11:14" x14ac:dyDescent="0.3">
-      <c r="K58" s="2">
-        <v>7723</v>
-      </c>
-      <c r="L58">
-        <f>K58/26.2598</f>
-        <v>294.09972657826796</v>
-      </c>
-      <c r="N58">
-        <v>21934</v>
-      </c>
-    </row>
-    <row r="59" spans="11:14" x14ac:dyDescent="0.3">
-      <c r="N59">
-        <v>149100.65359500001</v>
-      </c>
-    </row>
-    <row r="60" spans="11:14" x14ac:dyDescent="0.3">
-      <c r="N60">
-        <v>78475</v>
-      </c>
-    </row>
-    <row r="61" spans="11:14" x14ac:dyDescent="0.3">
-      <c r="N61">
-        <v>98782.28</v>
-      </c>
-    </row>
-    <row r="62" spans="11:14" x14ac:dyDescent="0.3">
-      <c r="N62">
-        <v>8836.83</v>
-      </c>
-    </row>
-    <row r="63" spans="11:14" x14ac:dyDescent="0.3">
-      <c r="N63">
-        <v>78333.224138000005</v>
-      </c>
-    </row>
-    <row r="64" spans="11:14" x14ac:dyDescent="0.3">
-      <c r="N64">
-        <v>8000</v>
-      </c>
-    </row>
-    <row r="65" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N65">
-        <v>13650</v>
-      </c>
-    </row>
-    <row r="66" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N66">
-        <v>5853</v>
-      </c>
-    </row>
-    <row r="67" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N67">
-        <v>19827.428571</v>
-      </c>
-    </row>
-    <row r="68" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N68">
-        <v>8058.9989999999998</v>
-      </c>
-    </row>
-    <row r="69" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N69">
-        <v>6400</v>
-      </c>
-    </row>
-    <row r="70" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N72">
-        <v>5040</v>
-      </c>
-    </row>
-    <row r="73" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N73">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="74" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N74">
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="75" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N75">
-        <v>2820</v>
-      </c>
-    </row>
-    <row r="76" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N76">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N77">
-        <v>4743.6660000000002</v>
-      </c>
-    </row>
-    <row r="78" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N79">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N80">
-        <v>7125</v>
-      </c>
-    </row>
-    <row r="81" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N82">
-        <v>81579.12</v>
-      </c>
-    </row>
-    <row r="83" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N83">
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="84" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N84">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="85" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N85">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="86" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N86">
-        <v>139.13999999999999</v>
-      </c>
-    </row>
-    <row r="87" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N87">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="88" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N88">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="89" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N89">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="90" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N90">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N91">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N92">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N93">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N94">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N95">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N96">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N97">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N98">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N99">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N100">
-        <v>2640</v>
-      </c>
-    </row>
-    <row r="101" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N101">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N102">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N103">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N104">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N105">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N106">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N107">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N108">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N109">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N110">
-        <v>36630</v>
-      </c>
-    </row>
-    <row r="111" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N111">
-        <v>7560</v>
-      </c>
-    </row>
-    <row r="112" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N112">
-        <v>8550</v>
-      </c>
+      <c r="C41" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C42" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="E42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K58" s="2"/>
     </row>
     <row r="113" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N113" s="6">
-        <f>SUM(N55:N112)</f>
-        <v>899850.74130399991</v>
-      </c>
+      <c r="N113" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1661,12 +1707,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A3E3F36-FCD2-4D59-81CE-AA1D1D1D0627}">
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
@@ -1807,7 +1853,7 @@
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B14" s="17">
+      <c r="B14" s="16">
         <v>1110104</v>
       </c>
       <c r="F14">
@@ -1862,7 +1908,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B17" s="11" t="s">
         <v>59</v>
       </c>
@@ -1879,48 +1925,177 @@
       </c>
       <c r="H17" s="12"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
-      <c r="G18" s="16">
+      <c r="G18" s="15">
         <v>-7500</v>
       </c>
       <c r="J18" s="9"/>
       <c r="K18" s="13"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="K19" s="6"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
       <c r="G21" s="6"/>
       <c r="H21" s="9"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="N21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D22" s="6"/>
       <c r="E22" s="2"/>
       <c r="H22" s="13"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="N22">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="G23" s="2"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="N23">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F25" s="6"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="N25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="6"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="N26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N27">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N28">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N29">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F30" s="9"/>
+      <c r="N30">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N31">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N32">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N33">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N34">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N36">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N37">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N38">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N39">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N40">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N41">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N42">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="43" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N43">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N44">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N45">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N46">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N47">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N48">
+        <f>SUM(N21:N47)</f>
+        <v>524</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1928,16 +2103,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BA96DCF-5607-4643-8615-E51DE316F486}">
   <dimension ref="A1:J162"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -4510,4 +4685,301 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A1A91D3-643F-4BB9-8D03-CCEBAAE4D8FC}">
+  <dimension ref="A1:I429"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>1</v>
+      </c>
+      <c r="B1">
+        <v>504.3</v>
+      </c>
+      <c r="C1">
+        <f>B1*A1</f>
+        <v>504.3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>504.3</v>
+      </c>
+      <c r="C2">
+        <f t="shared" ref="C2:C11" si="0">B2*A2</f>
+        <v>504.3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>504.3</v>
+      </c>
+      <c r="C3">
+        <f t="shared" si="0"/>
+        <v>504.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>504.3</v>
+      </c>
+      <c r="C4">
+        <f t="shared" si="0"/>
+        <v>504.3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>504.3</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="0"/>
+        <v>504.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>504.3</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="0"/>
+        <v>504.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>504.3</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="0"/>
+        <v>504.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>504.3</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>504.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>504.3</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="0"/>
+        <v>504.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>504.3</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="0"/>
+        <v>504.3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <v>504.3</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="0"/>
+        <v>504.3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <f>SUM(A1:A11)</f>
+        <v>11</v>
+      </c>
+      <c r="C12">
+        <f>SUM(C1:C11)</f>
+        <v>5547.3000000000011</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>504.3</v>
+      </c>
+      <c r="C13">
+        <f>A13*B13</f>
+        <v>1008.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14">
+        <v>504.3</v>
+      </c>
+      <c r="C14">
+        <f t="shared" ref="C14:C17" si="1">A14*B14</f>
+        <v>1008.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>4</v>
+      </c>
+      <c r="B15">
+        <v>504.3</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="1"/>
+        <v>2017.2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
+        <v>504.3</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="1"/>
+        <v>1008.6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17">
+        <v>504.3</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="1"/>
+        <v>504.3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <f>SUM(A13:A17)</f>
+        <v>11</v>
+      </c>
+      <c r="C18">
+        <f>SUM(C13:C17)</f>
+        <v>5547.3</v>
+      </c>
+    </row>
+    <row r="421" spans="6:9" x14ac:dyDescent="0.3">
+      <c r="F421" t="s">
+        <v>179</v>
+      </c>
+      <c r="G421" t="s">
+        <v>180</v>
+      </c>
+      <c r="H421" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="422" spans="6:9" x14ac:dyDescent="0.3">
+      <c r="F422">
+        <v>100</v>
+      </c>
+      <c r="G422">
+        <v>100</v>
+      </c>
+      <c r="H422">
+        <f>F422*G422</f>
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="423" spans="6:9" x14ac:dyDescent="0.3">
+      <c r="F423">
+        <v>100</v>
+      </c>
+      <c r="G423">
+        <v>200</v>
+      </c>
+      <c r="H423">
+        <f>F423*G423</f>
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="424" spans="6:9" x14ac:dyDescent="0.3">
+      <c r="F424">
+        <v>-50</v>
+      </c>
+      <c r="G424">
+        <v>100</v>
+      </c>
+      <c r="H424">
+        <f>F424*G424</f>
+        <v>-5000</v>
+      </c>
+    </row>
+    <row r="425" spans="6:9" x14ac:dyDescent="0.3">
+      <c r="F425">
+        <v>-100</v>
+      </c>
+      <c r="G425">
+        <v>200</v>
+      </c>
+      <c r="H425">
+        <f>F425*G425</f>
+        <v>-20000</v>
+      </c>
+    </row>
+    <row r="427" spans="6:9" x14ac:dyDescent="0.3">
+      <c r="F427">
+        <f>SUM(F422:F426)</f>
+        <v>50</v>
+      </c>
+      <c r="H427">
+        <f>SUM(H422:H426)</f>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="429" spans="6:9" x14ac:dyDescent="0.3">
+      <c r="I429" s="19">
+        <f>H427/F427</f>
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/textos/CONTROL DE CAMBIOS APARTIR DE LA 6.3.1.xlsx
+++ b/textos/CONTROL DE CAMBIOS APARTIR DE LA 6.3.1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\HOME OFFICE\ERP- COMEGCEN - SEMUBI - FLOR\ERP - SISC\ERP\textos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\HOME OFFICE\ERP- COMEGCEN - SEMUBI - FLOR\ERP - SISC\ERP\textos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11918F68-7602-441C-BA1F-A2B4B3F3994B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3667AA27-26BC-4CB2-A8D9-44CC3C95704C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CASOS ERP" sheetId="4" r:id="rId1"/>
@@ -36,12 +36,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="195">
   <si>
     <t xml:space="preserve">CONTRO DE CAMBIOS DE ERP SISC </t>
   </si>
@@ -593,6 +596,39 @@
   </si>
   <si>
     <t>se interpolo los vales en el reporte para que cuadren saldos</t>
+  </si>
+  <si>
+    <t>6.5.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m_repor_invn </t>
+  </si>
+  <si>
+    <t>se arreglo el ultimo costo a la fecha</t>
+  </si>
+  <si>
+    <t>exportacion a excel conforme a nuevo reporte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">se agrego botones y arreglo encabezado </t>
+  </si>
+  <si>
+    <t>w_costo_promedio</t>
+  </si>
+  <si>
+    <t>12,1</t>
+  </si>
+  <si>
+    <t>w_select_rep_i</t>
+  </si>
+  <si>
+    <t>se cambio costo de venta por preciod e venta</t>
+  </si>
+  <si>
+    <t>R_KARDEX</t>
+  </si>
+  <si>
+    <t>AGREGARON CAMPOS</t>
   </si>
 </sst>
 </file>
@@ -600,8 +636,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="44" formatCode="_-&quot;L&quot;* #,##0.00_-;\-&quot;L&quot;* #,##0.00_-;_-&quot;L&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;L&quot;* #,##0.00_-;\-&quot;L&quot;* #,##0.00_-;_-&quot;L&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -683,7 +719,7 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -694,26 +730,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
@@ -997,15 +1033,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50EBBD9B-B973-419E-B723-706D7A196B5A}">
   <dimension ref="A3:F23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="61.44140625" customWidth="1"/>
-    <col min="2" max="2" width="38.33203125" customWidth="1"/>
+    <col min="1" max="1" width="61.42578125" customWidth="1"/>
+    <col min="2" max="2" width="38.28515625" customWidth="1"/>
     <col min="3" max="3" width="59" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>173</v>
       </c>
@@ -1019,7 +1055,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>150</v>
       </c>
@@ -1033,7 +1069,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>153</v>
       </c>
@@ -1045,7 +1081,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>177</v>
       </c>
@@ -1059,7 +1095,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>156</v>
       </c>
@@ -1073,7 +1109,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>159</v>
       </c>
@@ -1087,7 +1123,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>162</v>
       </c>
@@ -1098,7 +1134,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>165</v>
       </c>
@@ -1112,7 +1148,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>168</v>
       </c>
@@ -1126,7 +1162,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>171</v>
       </c>
@@ -1140,7 +1176,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F23" s="2">
         <v>1248848.4099999999</v>
       </c>
@@ -1153,110 +1189,110 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P113"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="5" customWidth="1"/>
-    <col min="3" max="3" width="48.33203125" customWidth="1"/>
-    <col min="4" max="4" width="39.33203125" customWidth="1"/>
-    <col min="5" max="5" width="10.33203125" customWidth="1"/>
-    <col min="6" max="6" width="22.33203125" customWidth="1"/>
-    <col min="8" max="8" width="13.109375" customWidth="1"/>
-    <col min="14" max="14" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.28515625" customWidth="1"/>
+    <col min="4" max="4" width="39.28515625" customWidth="1"/>
+    <col min="5" max="5" width="10.28515625" customWidth="1"/>
+    <col min="6" max="6" width="22.28515625" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" customWidth="1"/>
+    <col min="14" max="14" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="18"/>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="18"/>
-      <c r="M3" s="18"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="18"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="18"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18"/>
-      <c r="L5" s="18"/>
-      <c r="M5" s="18"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="18"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="19"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="19"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="19"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
+      <c r="M5" s="19"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>1</v>
       </c>
@@ -1274,7 +1310,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -1286,7 +1322,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6.4</v>
       </c>
@@ -1300,7 +1336,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C10" s="5" t="s">
         <v>9</v>
       </c>
@@ -1312,7 +1348,7 @@
       </c>
       <c r="H10" s="2"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C11" s="5" t="s">
         <v>10</v>
       </c>
@@ -1323,7 +1359,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C12" s="5" t="s">
         <v>12</v>
       </c>
@@ -1335,7 +1371,7 @@
       </c>
       <c r="H12" s="2"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>13</v>
       </c>
@@ -1347,7 +1383,7 @@
       </c>
       <c r="H13" s="2"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>13</v>
       </c>
@@ -1359,7 +1395,7 @@
       </c>
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>13</v>
       </c>
@@ -1371,7 +1407,7 @@
       </c>
       <c r="H15" s="2"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C16" s="5" t="s">
         <v>21</v>
       </c>
@@ -1386,7 +1422,7 @@
       </c>
       <c r="H16" s="2"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C17" s="5" t="s">
         <v>23</v>
       </c>
@@ -1394,7 +1430,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C18" s="5" t="s">
         <v>24</v>
       </c>
@@ -1405,7 +1441,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>13</v>
       </c>
@@ -1416,7 +1452,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
         <v>27</v>
       </c>
@@ -1424,7 +1460,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>13</v>
       </c>
@@ -1438,7 +1474,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
         <v>33</v>
       </c>
@@ -1449,7 +1485,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C23" s="5" t="s">
         <v>36</v>
       </c>
@@ -1460,7 +1496,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C24" s="5" t="s">
         <v>23</v>
       </c>
@@ -1468,7 +1504,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C25" s="5" t="s">
         <v>40</v>
       </c>
@@ -1482,7 +1518,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>50</v>
       </c>
@@ -1499,7 +1535,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C27" s="5" t="s">
         <v>53</v>
       </c>
@@ -1510,7 +1546,7 @@
         <v>15101</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C28" s="5" t="s">
         <v>55</v>
       </c>
@@ -1521,7 +1557,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C29" s="5" t="s">
         <v>61</v>
       </c>
@@ -1535,7 +1571,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>13</v>
       </c>
@@ -1546,7 +1582,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C31" s="5" t="s">
         <v>66</v>
       </c>
@@ -1558,7 +1594,7 @@
       </c>
       <c r="M31" s="2"/>
     </row>
-    <row r="32" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>13</v>
       </c>
@@ -1569,7 +1605,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="33" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="C33" s="5" t="s">
         <v>118</v>
       </c>
@@ -1589,7 +1625,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C34" s="5" t="s">
         <v>133</v>
       </c>
@@ -1603,7 +1639,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C35" s="14" t="s">
         <v>136</v>
       </c>
@@ -1621,7 +1657,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="36" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>13</v>
       </c>
@@ -1639,7 +1675,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C37" s="5" t="s">
         <v>140</v>
       </c>
@@ -1650,7 +1686,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C38" s="5" t="s">
         <v>142</v>
       </c>
@@ -1661,7 +1697,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C39" s="5" t="s">
         <v>146</v>
       </c>
@@ -1669,12 +1705,12 @@
         <v>145</v>
       </c>
     </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C40" s="5" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C41" s="5" t="s">
         <v>149</v>
       </c>
@@ -1682,7 +1718,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="42" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="C42" s="5" t="s">
         <v>183</v>
       </c>
@@ -1693,10 +1729,87 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="11:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>184</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E44">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C45" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E45">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C46" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="E46" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C47" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="E47">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C48" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="J48">
+        <v>2</v>
+      </c>
+      <c r="K48">
+        <v>29.56</v>
+      </c>
+      <c r="L48">
+        <f>J48*K48</f>
+        <v>59.12</v>
+      </c>
+    </row>
+    <row r="49" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J49">
+        <v>3</v>
+      </c>
+      <c r="K49">
+        <v>104.34</v>
+      </c>
+      <c r="L49">
+        <f>J49*K49</f>
+        <v>313.02</v>
+      </c>
+    </row>
+    <row r="58" spans="10:12" x14ac:dyDescent="0.25">
       <c r="K58" s="2"/>
     </row>
-    <row r="113" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="113" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N113" s="6"/>
     </row>
   </sheetData>
@@ -1710,20 +1823,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A3E3F36-FCD2-4D59-81CE-AA1D1D1D0627}">
   <dimension ref="A1:N48"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B1">
         <v>0</v>
       </c>
@@ -1735,7 +1848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2">
         <v>22</v>
       </c>
@@ -1757,7 +1870,7 @@
         <v>1614.08</v>
       </c>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3">
         <v>100</v>
       </c>
@@ -1779,7 +1892,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>5</v>
       </c>
@@ -1801,7 +1914,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="7">
         <f>SUM(B1:B4)</f>
         <v>127</v>
@@ -1827,16 +1940,16 @@
         <v>3414.08</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C6" s="9"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D7" s="9">
         <f>D5/B5</f>
         <v>813.24629921259839</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9">
         <f>B5-F5</f>
         <v>123</v>
@@ -1846,13 +1959,13 @@
         <v>99868.2</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D11" s="9">
         <f>D9/B9</f>
         <v>811.9365853658536</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="16">
         <v>1110104</v>
       </c>
@@ -1864,7 +1977,7 @@
         <v>1128432.67</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>57</v>
       </c>
@@ -1888,7 +2001,7 @@
         <v>1165892.92</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>58</v>
       </c>
@@ -1908,7 +2021,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B17" s="11" t="s">
         <v>59</v>
       </c>
@@ -1925,7 +2038,7 @@
       </c>
       <c r="H17" s="12"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
       <c r="G18" s="15">
@@ -1934,16 +2047,16 @@
       <c r="J18" s="9"/>
       <c r="K18" s="13"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="K19" s="6"/>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
       <c r="G21" s="6"/>
@@ -1952,7 +2065,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D22" s="6"/>
       <c r="E22" s="2"/>
       <c r="H22" s="13"/>
@@ -1960,24 +2073,24 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="G23" s="2"/>
       <c r="N23">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="N24">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F25" s="6"/>
       <c r="N25">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="6"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -1985,113 +2098,113 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="N27">
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="N28">
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="N29">
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F30" s="9"/>
       <c r="N30">
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="N31">
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="N32">
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N33">
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N34">
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N35">
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N36">
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N37">
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N38">
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N39">
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N40">
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N41">
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N42">
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N43">
         <v>30</v>
       </c>
     </row>
-    <row r="44" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N44">
         <v>30</v>
       </c>
     </row>
-    <row r="45" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="45" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N45">
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="46" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N46">
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N47">
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N48">
         <f>SUM(N21:N47)</f>
         <v>524</v>
@@ -2106,16 +2219,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BA96DCF-5607-4643-8615-E51DE316F486}">
   <dimension ref="A1:J162"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1">
         <v>310000085</v>
       </c>
@@ -2139,7 +2252,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>310000084</v>
       </c>
@@ -2167,7 +2280,7 @@
         <v>2850</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>310000083</v>
       </c>
@@ -2195,7 +2308,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>310000082</v>
       </c>
@@ -2223,7 +2336,7 @@
         <v>2091</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>310000081</v>
       </c>
@@ -2251,7 +2364,7 @@
         <v>9900</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>310000081</v>
       </c>
@@ -2279,7 +2392,7 @@
         <v>652.1739</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>310000080</v>
       </c>
@@ -2307,7 +2420,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>310000079</v>
       </c>
@@ -2335,7 +2448,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>310000078</v>
       </c>
@@ -2363,7 +2476,7 @@
         <v>3015</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>310000077</v>
       </c>
@@ -2391,7 +2504,7 @@
         <v>50400</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>310000076</v>
       </c>
@@ -2419,7 +2532,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>310000075</v>
       </c>
@@ -2447,7 +2560,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>310000071</v>
       </c>
@@ -2475,7 +2588,7 @@
         <v>8350</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>310000069</v>
       </c>
@@ -2503,7 +2616,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>310000066</v>
       </c>
@@ -2531,7 +2644,7 @@
         <v>2520</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>310000065</v>
       </c>
@@ -2559,7 +2672,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>310000059</v>
       </c>
@@ -2587,7 +2700,7 @@
         <v>365.21999999999997</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>310000058</v>
       </c>
@@ -2615,7 +2728,7 @@
         <v>504.36</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>310000056</v>
       </c>
@@ -2643,7 +2756,7 @@
         <v>434.8</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>310000055</v>
       </c>
@@ -2671,7 +2784,7 @@
         <v>326.08499999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>310000054</v>
       </c>
@@ -2699,7 +2812,7 @@
         <v>326.09250000000003</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>310000054</v>
       </c>
@@ -2727,7 +2840,7 @@
         <v>22.61</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>310000054</v>
       </c>
@@ -2755,7 +2868,7 @@
         <v>104.34</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>310000053</v>
       </c>
@@ -2783,7 +2896,7 @@
         <v>339.12</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>310000051</v>
       </c>
@@ -2811,7 +2924,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>310000050</v>
       </c>
@@ -2839,7 +2952,7 @@
         <v>208.70999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>310000045</v>
       </c>
@@ -2867,7 +2980,7 @@
         <v>1664.88</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>310000044</v>
       </c>
@@ -2895,7 +3008,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>310000043</v>
       </c>
@@ -2923,7 +3036,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>310000042</v>
       </c>
@@ -2951,7 +3064,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>310000041</v>
       </c>
@@ -2979,7 +3092,7 @@
         <v>330.44</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>310000040</v>
       </c>
@@ -3007,7 +3120,7 @@
         <v>1236.9960000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>310000039</v>
       </c>
@@ -3035,7 +3148,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>310000038</v>
       </c>
@@ -3063,7 +3176,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>310000036</v>
       </c>
@@ -3091,7 +3204,7 @@
         <v>2874</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>310000036</v>
       </c>
@@ -3119,7 +3232,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>310000035</v>
       </c>
@@ -3147,7 +3260,7 @@
         <v>3200</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>310000033</v>
       </c>
@@ -3175,7 +3288,7 @@
         <v>3304.5709999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>310000026</v>
       </c>
@@ -3203,7 +3316,7 @@
         <v>3902</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>310000025</v>
       </c>
@@ -3231,7 +3344,7 @@
         <v>13650</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>310000025</v>
       </c>
@@ -3259,7 +3372,7 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>310000024</v>
       </c>
@@ -3287,7 +3400,7 @@
         <v>5923.36</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>310000023</v>
       </c>
@@ -3315,7 +3428,7 @@
         <v>732.08600000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>310000023</v>
       </c>
@@ -3343,7 +3456,7 @@
         <v>11526.3</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>310000021</v>
       </c>
@@ -3371,7 +3484,7 @@
         <v>10750</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>310000020</v>
       </c>
@@ -3399,7 +3512,7 @@
         <v>170275</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>310000019</v>
       </c>
@@ -3427,7 +3540,7 @@
         <v>24925</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>310000018</v>
       </c>
@@ -3455,7 +3568,7 @@
         <v>39683.600000000006</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>310000017</v>
       </c>
@@ -3483,7 +3596,7 @@
         <v>15522</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>310000016</v>
       </c>
@@ -3511,7 +3624,7 @@
         <v>47355</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>310000015</v>
       </c>
@@ -3530,7 +3643,7 @@
         <v>477584.74439999997</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>310000014</v>
       </c>
@@ -3545,7 +3658,7 @@
         <v>3200</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>310000014</v>
       </c>
@@ -3560,7 +3673,7 @@
         <v>19932</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>310000013</v>
       </c>
@@ -3575,7 +3688,7 @@
         <v>9755</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>310000012</v>
       </c>
@@ -3590,7 +3703,7 @@
         <v>27300</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>310000011</v>
       </c>
@@ -3605,7 +3718,7 @@
         <v>32000</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>310000010</v>
       </c>
@@ -3620,7 +3733,7 @@
         <v>10880</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>310000010</v>
       </c>
@@ -3635,7 +3748,7 @@
         <v>74042</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>310000009</v>
       </c>
@@ -3650,7 +3763,7 @@
         <v>20363.129999999997</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>310000007</v>
       </c>
@@ -3665,7 +3778,7 @@
         <v>80704</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>310000007</v>
       </c>
@@ -3680,7 +3793,7 @@
         <v>18078.28</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>310000006</v>
       </c>
@@ -3695,7 +3808,7 @@
         <v>89225</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>310000005</v>
       </c>
@@ -3710,7 +3823,7 @@
         <v>111300</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>310000005</v>
       </c>
@@ -3729,7 +3842,7 @@
         <v>900208.41800000006</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>310000004</v>
       </c>
@@ -3744,7 +3857,7 @@
         <v>46859</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>310000003</v>
       </c>
@@ -3759,7 +3872,7 @@
         <v>64999.000000000007</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>310000002</v>
       </c>
@@ -3774,7 +3887,7 @@
         <v>78804</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>310000001</v>
       </c>
@@ -3789,13 +3902,13 @@
         <v>192495</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D69" s="6">
         <f>SUM(D1:D68)</f>
         <v>1377793.1624</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="H72">
         <v>-3300</v>
       </c>
@@ -3803,7 +3916,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B73" s="6"/>
       <c r="H73">
         <v>-2091</v>
@@ -3812,7 +3925,7 @@
         <v>22.61</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="H74">
         <v>20</v>
       </c>
@@ -3820,7 +3933,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="H75">
         <v>22.61</v>
       </c>
@@ -3828,7 +3941,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="H76">
         <v>100</v>
       </c>
@@ -3836,7 +3949,7 @@
         <v>104.34</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="H77">
         <v>100</v>
       </c>
@@ -3844,7 +3957,7 @@
         <v>121.74</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="H78">
         <v>104.34</v>
       </c>
@@ -3852,7 +3965,7 @@
         <v>121.74</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="H79">
         <v>121.74</v>
       </c>
@@ -3860,7 +3973,7 @@
         <v>121.74</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="H80">
         <v>121.74</v>
       </c>
@@ -3868,7 +3981,7 @@
         <v>126.09</v>
       </c>
     </row>
-    <row r="81" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H81">
         <v>121.74</v>
       </c>
@@ -3876,7 +3989,7 @@
         <v>126.09</v>
       </c>
     </row>
-    <row r="82" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H82">
         <v>126.09</v>
       </c>
@@ -3884,7 +3997,7 @@
         <v>126.09</v>
       </c>
     </row>
-    <row r="83" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H83">
         <v>126.09</v>
       </c>
@@ -3892,7 +4005,7 @@
         <v>126.09</v>
       </c>
     </row>
-    <row r="84" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H84">
         <v>126.09</v>
       </c>
@@ -3900,7 +4013,7 @@
         <v>165.22</v>
       </c>
     </row>
-    <row r="85" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="85" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H85">
         <v>126.09</v>
       </c>
@@ -3908,7 +4021,7 @@
         <v>165.22</v>
       </c>
     </row>
-    <row r="86" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="86" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H86">
         <v>139.13999999999999</v>
       </c>
@@ -3916,7 +4029,7 @@
         <v>208.71</v>
       </c>
     </row>
-    <row r="87" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="87" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H87">
         <v>160</v>
       </c>
@@ -3924,7 +4037,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="88" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="88" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H88">
         <v>165.22</v>
       </c>
@@ -3932,7 +4045,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="89" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="89" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H89">
         <v>165.22</v>
       </c>
@@ -3940,7 +4053,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="90" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="90" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H90">
         <v>208.71</v>
       </c>
@@ -3948,7 +4061,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="91" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="91" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H91">
         <v>220</v>
       </c>
@@ -3956,7 +4069,7 @@
         <v>326.08499999999998</v>
       </c>
     </row>
-    <row r="92" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="92" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H92">
         <v>220</v>
       </c>
@@ -3964,7 +4077,7 @@
         <v>326.09249999999997</v>
       </c>
     </row>
-    <row r="93" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="93" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H93">
         <v>320</v>
       </c>
@@ -3972,7 +4085,7 @@
         <v>339.12</v>
       </c>
     </row>
-    <row r="94" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="94" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H94">
         <v>326.08499999999998</v>
       </c>
@@ -3980,7 +4093,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="95" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="95" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H95">
         <v>326.09249999999997</v>
       </c>
@@ -3988,7 +4101,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="96" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="96" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H96">
         <v>339.12</v>
       </c>
@@ -3996,7 +4109,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="97" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="97" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H97">
         <v>350</v>
       </c>
@@ -4004,7 +4117,7 @@
         <v>384.21</v>
       </c>
     </row>
-    <row r="98" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="98" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H98">
         <v>350</v>
       </c>
@@ -4012,7 +4125,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="99" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="99" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H99">
         <v>385</v>
       </c>
@@ -4020,7 +4133,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="100" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="100" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H100">
         <v>434.8</v>
       </c>
@@ -4028,7 +4141,7 @@
         <v>434.8</v>
       </c>
     </row>
-    <row r="101" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="101" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H101">
         <v>440</v>
       </c>
@@ -4036,7 +4149,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="102" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="102" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H102">
         <v>440</v>
       </c>
@@ -4044,7 +4157,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="103" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="103" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H103">
         <v>470</v>
       </c>
@@ -4052,7 +4165,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="104" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="104" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H104">
         <v>630</v>
       </c>
@@ -4060,7 +4173,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="105" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="105" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H105">
         <v>630</v>
       </c>
@@ -4068,7 +4181,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="106" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="106" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H106">
         <v>652.1739</v>
       </c>
@@ -4076,7 +4189,7 @@
         <v>652.1739</v>
       </c>
     </row>
-    <row r="107" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="107" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H107">
         <v>663.66600000000005</v>
       </c>
@@ -4084,7 +4197,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="108" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="108" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H108">
         <v>675</v>
       </c>
@@ -4092,7 +4205,7 @@
         <v>684.2</v>
       </c>
     </row>
-    <row r="109" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="109" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H109">
         <v>750</v>
       </c>
@@ -4100,7 +4213,7 @@
         <v>732.08600000000001</v>
       </c>
     </row>
-    <row r="110" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="110" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H110">
         <v>790</v>
       </c>
@@ -4108,7 +4221,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="111" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="111" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H111">
         <v>840</v>
       </c>
@@ -4116,7 +4229,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="112" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="112" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H112">
         <v>880</v>
       </c>
@@ -4124,7 +4237,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="113" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="113" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H113">
         <v>900</v>
       </c>
@@ -4132,7 +4245,7 @@
         <v>832.44</v>
       </c>
     </row>
-    <row r="114" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="114" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H114">
         <v>912</v>
       </c>
@@ -4140,7 +4253,7 @@
         <v>832.44</v>
       </c>
     </row>
-    <row r="115" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="115" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H115">
         <v>1236.9960000000001</v>
       </c>
@@ -4148,7 +4261,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="116" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="116" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H116">
         <v>1260</v>
       </c>
@@ -4156,7 +4269,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="117" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="117" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H117">
         <v>1260</v>
       </c>
@@ -4164,7 +4277,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="118" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="118" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H118">
         <v>1260</v>
       </c>
@@ -4172,7 +4285,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="119" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="119" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H119">
         <v>1750</v>
       </c>
@@ -4180,7 +4293,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="120" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="120" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H120">
         <v>1800</v>
       </c>
@@ -4188,7 +4301,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="121" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="121" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H121">
         <v>1908</v>
       </c>
@@ -4196,7 +4309,7 @@
         <v>1236.9960000000001</v>
       </c>
     </row>
-    <row r="122" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="122" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H122">
         <v>2091</v>
       </c>
@@ -4204,7 +4317,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="123" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="123" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H123">
         <v>2091</v>
       </c>
@@ -4212,7 +4325,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="124" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="124" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H124">
         <v>2640</v>
       </c>
@@ -4220,7 +4333,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="125" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="125" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H125">
         <v>2874</v>
       </c>
@@ -4228,7 +4341,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="126" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="126" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H126">
         <v>3015</v>
       </c>
@@ -4236,7 +4349,7 @@
         <v>1921.05</v>
       </c>
     </row>
-    <row r="127" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="127" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H127">
         <v>3200</v>
       </c>
@@ -4244,7 +4357,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="128" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="128" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H128">
         <v>3300</v>
       </c>
@@ -4252,7 +4365,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="129" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="129" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H129">
         <v>3300</v>
       </c>
@@ -4260,7 +4373,7 @@
         <v>2091</v>
       </c>
     </row>
-    <row r="130" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="130" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H130">
         <v>4000</v>
       </c>
@@ -4268,7 +4381,7 @@
         <v>2850</v>
       </c>
     </row>
-    <row r="131" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="131" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H131">
         <v>4080</v>
       </c>
@@ -4276,7 +4389,7 @@
         <v>2991</v>
       </c>
     </row>
-    <row r="132" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="132" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H132">
         <v>4550</v>
       </c>
@@ -4284,7 +4397,7 @@
         <v>3015</v>
       </c>
     </row>
-    <row r="133" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="133" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H133">
         <v>5040</v>
       </c>
@@ -4292,7 +4405,7 @@
         <v>3200</v>
       </c>
     </row>
-    <row r="134" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="134" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H134">
         <v>6600</v>
       </c>
@@ -4300,7 +4413,7 @@
         <v>3300</v>
       </c>
     </row>
-    <row r="135" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="135" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H135">
         <v>7500</v>
       </c>
@@ -4308,7 +4421,7 @@
         <v>3304.5709999999999</v>
       </c>
     </row>
-    <row r="136" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="136" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H136">
         <v>7500</v>
       </c>
@@ -4316,7 +4429,7 @@
         <v>3582</v>
       </c>
     </row>
-    <row r="137" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="137" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H137">
         <v>7560</v>
       </c>
@@ -4324,7 +4437,7 @@
         <v>3690</v>
       </c>
     </row>
-    <row r="138" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="138" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H138">
         <v>8058.9989999999998</v>
       </c>
@@ -4332,7 +4445,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="139" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="139" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H139">
         <v>8350</v>
       </c>
@@ -4340,7 +4453,7 @@
         <v>4550</v>
       </c>
     </row>
-    <row r="140" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="140" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H140">
         <v>9600</v>
       </c>
@@ -4348,7 +4461,7 @@
         <v>4789.3999999999996</v>
       </c>
     </row>
-    <row r="141" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="141" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H141">
         <v>9755</v>
       </c>
@@ -4356,7 +4469,7 @@
         <v>4985</v>
       </c>
     </row>
-    <row r="142" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="142" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H142">
         <v>10880</v>
       </c>
@@ -4364,7 +4477,7 @@
         <v>5923.36</v>
       </c>
     </row>
-    <row r="143" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="143" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H143">
         <v>11400</v>
       </c>
@@ -4372,7 +4485,7 @@
         <v>5982</v>
       </c>
     </row>
-    <row r="144" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="144" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H144">
         <v>18078.28</v>
       </c>
@@ -4380,7 +4493,7 @@
         <v>6600</v>
       </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>119</v>
       </c>
@@ -4403,7 +4516,7 @@
         <v>6979</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>112</v>
       </c>
@@ -4430,7 +4543,7 @@
         <v>8350</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>112</v>
       </c>
@@ -4461,7 +4574,7 @@
         <v>9100</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>112</v>
       </c>
@@ -4492,7 +4605,7 @@
         <v>9221.0400000000009</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>112</v>
       </c>
@@ -4515,7 +4628,7 @@
         <v>10750</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>112</v>
       </c>
@@ -4538,7 +4651,7 @@
         <v>11940</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>112</v>
       </c>
@@ -4561,7 +4674,7 @@
         <v>12300</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>112</v>
       </c>
@@ -4584,7 +4697,7 @@
         <v>12510</v>
       </c>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>112</v>
       </c>
@@ -4607,7 +4720,7 @@
         <v>17375</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D154">
         <f>SUM(D146:D153)</f>
         <v>704</v>
@@ -4619,7 +4732,7 @@
         <v>20850</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="H155">
         <v>80704</v>
       </c>
@@ -4627,7 +4740,7 @@
         <v>22240</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="H156">
         <v>83244</v>
       </c>
@@ -4635,7 +4748,7 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="H157">
         <v>89225</v>
       </c>
@@ -4643,7 +4756,7 @@
         <v>27800</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="H158">
         <v>111300</v>
       </c>
@@ -4651,7 +4764,7 @@
         <v>30750</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="H159">
         <v>192495</v>
       </c>
@@ -4659,7 +4772,7 @@
         <v>34210</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
       <c r="H160">
         <v>208500</v>
       </c>
@@ -4667,7 +4780,7 @@
         <v>50400</v>
       </c>
     </row>
-    <row r="161" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="161" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H161" s="8">
         <f>SUM(H72:H160)</f>
         <v>1377793.1624</v>
@@ -4676,7 +4789,7 @@
         <v>69500</v>
       </c>
     </row>
-    <row r="162" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="162" spans="8:10" x14ac:dyDescent="0.25">
       <c r="J162" s="6">
         <f>SUM(J72:J161)</f>
         <v>477584.74439999997</v>
@@ -4690,9 +4803,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A1A91D3-643F-4BB9-8D03-CCEBAAE4D8FC}">
   <dimension ref="A1:I429"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1">
         <v>1</v>
       </c>
@@ -4704,7 +4817,7 @@
         <v>504.3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4716,7 +4829,7 @@
         <v>504.3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -4728,7 +4841,7 @@
         <v>504.3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -4740,7 +4853,7 @@
         <v>504.3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
@@ -4752,7 +4865,7 @@
         <v>504.3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1</v>
       </c>
@@ -4764,7 +4877,7 @@
         <v>504.3</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1</v>
       </c>
@@ -4776,7 +4889,7 @@
         <v>504.3</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1</v>
       </c>
@@ -4788,7 +4901,7 @@
         <v>504.3</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1</v>
       </c>
@@ -4800,7 +4913,7 @@
         <v>504.3</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1</v>
       </c>
@@ -4812,7 +4925,7 @@
         <v>504.3</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1</v>
       </c>
@@ -4824,7 +4937,7 @@
         <v>504.3</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>SUM(A1:A11)</f>
         <v>11</v>
@@ -4834,7 +4947,7 @@
         <v>5547.3000000000011</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2</v>
       </c>
@@ -4846,7 +4959,7 @@
         <v>1008.6</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2</v>
       </c>
@@ -4858,7 +4971,7 @@
         <v>1008.6</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>4</v>
       </c>
@@ -4870,7 +4983,7 @@
         <v>2017.2</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2</v>
       </c>
@@ -4882,7 +4995,7 @@
         <v>1008.6</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>1</v>
       </c>
@@ -4894,7 +5007,7 @@
         <v>504.3</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>SUM(A13:A17)</f>
         <v>11</v>
@@ -4904,7 +5017,7 @@
         <v>5547.3</v>
       </c>
     </row>
-    <row r="421" spans="6:9" x14ac:dyDescent="0.3">
+    <row r="421" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F421" t="s">
         <v>179</v>
       </c>
@@ -4915,7 +5028,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="422" spans="6:9" x14ac:dyDescent="0.3">
+    <row r="422" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F422">
         <v>100</v>
       </c>
@@ -4927,7 +5040,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="423" spans="6:9" x14ac:dyDescent="0.3">
+    <row r="423" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F423">
         <v>100</v>
       </c>
@@ -4939,7 +5052,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="424" spans="6:9" x14ac:dyDescent="0.3">
+    <row r="424" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F424">
         <v>-50</v>
       </c>
@@ -4951,7 +5064,7 @@
         <v>-5000</v>
       </c>
     </row>
-    <row r="425" spans="6:9" x14ac:dyDescent="0.3">
+    <row r="425" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F425">
         <v>-100</v>
       </c>
@@ -4963,7 +5076,7 @@
         <v>-20000</v>
       </c>
     </row>
-    <row r="427" spans="6:9" x14ac:dyDescent="0.3">
+    <row r="427" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F427">
         <f>SUM(F422:F426)</f>
         <v>50</v>
@@ -4973,8 +5086,8 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="429" spans="6:9" x14ac:dyDescent="0.3">
-      <c r="I429" s="19">
+    <row r="429" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="I429" s="18">
         <f>H427/F427</f>
         <v>100</v>
       </c>

--- a/textos/CONTROL DE CAMBIOS APARTIR DE LA 6.3.1.xlsx
+++ b/textos/CONTROL DE CAMBIOS APARTIR DE LA 6.3.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\HOME OFFICE\ERP- COMEGCEN - SEMUBI - FLOR\ERP - SISC\ERP\textos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3667AA27-26BC-4CB2-A8D9-44CC3C95704C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C870CBE-49DA-4064-BE88-82FC65ADE70A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2070" yWindow="3555" windowWidth="31275" windowHeight="10620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CASOS ERP" sheetId="4" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="197">
   <si>
     <t xml:space="preserve">CONTRO DE CAMBIOS DE ERP SISC </t>
   </si>
@@ -629,6 +629,12 @@
   </si>
   <si>
     <t>AGREGARON CAMPOS</t>
+  </si>
+  <si>
+    <t>w_bod_add_detalle_sal</t>
+  </si>
+  <si>
+    <t>cambiar ultimo costo</t>
   </si>
 </sst>
 </file>
@@ -1033,15 +1039,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50EBBD9B-B973-419E-B723-706D7A196B5A}">
   <dimension ref="A3:F23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="61.42578125" customWidth="1"/>
-    <col min="2" max="2" width="38.28515625" customWidth="1"/>
+    <col min="1" max="1" width="61.44140625" customWidth="1"/>
+    <col min="2" max="2" width="38.33203125" customWidth="1"/>
     <col min="3" max="3" width="59" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>173</v>
       </c>
@@ -1055,7 +1061,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>150</v>
       </c>
@@ -1069,7 +1075,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>153</v>
       </c>
@@ -1081,7 +1087,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>177</v>
       </c>
@@ -1095,7 +1101,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>156</v>
       </c>
@@ -1109,7 +1115,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>159</v>
       </c>
@@ -1123,7 +1129,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>162</v>
       </c>
@@ -1134,7 +1140,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>165</v>
       </c>
@@ -1148,7 +1154,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>168</v>
       </c>
@@ -1162,7 +1168,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>171</v>
       </c>
@@ -1176,7 +1182,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F23" s="2">
         <v>1248848.4099999999</v>
       </c>
@@ -1189,18 +1195,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P113"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="5" customWidth="1"/>
-    <col min="3" max="3" width="48.28515625" customWidth="1"/>
-    <col min="4" max="4" width="39.28515625" customWidth="1"/>
-    <col min="5" max="5" width="10.28515625" customWidth="1"/>
-    <col min="6" max="6" width="22.28515625" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" customWidth="1"/>
-    <col min="14" max="14" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.33203125" customWidth="1"/>
+    <col min="4" max="4" width="39.33203125" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" customWidth="1"/>
+    <col min="6" max="6" width="22.33203125" customWidth="1"/>
+    <col min="8" max="8" width="13.109375" customWidth="1"/>
+    <col min="14" max="14" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1217,7 +1223,7 @@
       <c r="L1" s="19"/>
       <c r="M1" s="19"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="19"/>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
@@ -1232,7 +1238,7 @@
       <c r="L2" s="19"/>
       <c r="M2" s="19"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="19"/>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
@@ -1247,7 +1253,7 @@
       <c r="L3" s="19"/>
       <c r="M3" s="19"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="19"/>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -1262,7 +1268,7 @@
       <c r="L4" s="19"/>
       <c r="M4" s="19"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="19"/>
       <c r="B5" s="19"/>
       <c r="C5" s="19"/>
@@ -1277,7 +1283,7 @@
       <c r="L5" s="19"/>
       <c r="M5" s="19"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="19"/>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
@@ -1292,7 +1298,7 @@
       <c r="L6" s="19"/>
       <c r="M6" s="19"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>1</v>
       </c>
@@ -1310,7 +1316,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -1322,7 +1328,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>6.4</v>
       </c>
@@ -1336,7 +1342,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C10" s="5" t="s">
         <v>9</v>
       </c>
@@ -1348,7 +1354,7 @@
       </c>
       <c r="H10" s="2"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C11" s="5" t="s">
         <v>10</v>
       </c>
@@ -1359,7 +1365,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C12" s="5" t="s">
         <v>12</v>
       </c>
@@ -1371,7 +1377,7 @@
       </c>
       <c r="H12" s="2"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>13</v>
       </c>
@@ -1383,7 +1389,7 @@
       </c>
       <c r="H13" s="2"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>13</v>
       </c>
@@ -1395,7 +1401,7 @@
       </c>
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>13</v>
       </c>
@@ -1407,7 +1413,7 @@
       </c>
       <c r="H15" s="2"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C16" s="5" t="s">
         <v>21</v>
       </c>
@@ -1422,7 +1428,7 @@
       </c>
       <c r="H16" s="2"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C17" s="5" t="s">
         <v>23</v>
       </c>
@@ -1430,7 +1436,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C18" s="5" t="s">
         <v>24</v>
       </c>
@@ -1441,7 +1447,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>13</v>
       </c>
@@ -1452,7 +1458,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C20" s="5" t="s">
         <v>27</v>
       </c>
@@ -1460,7 +1466,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>13</v>
       </c>
@@ -1474,7 +1480,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C22" s="5" t="s">
         <v>33</v>
       </c>
@@ -1485,7 +1491,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C23" s="5" t="s">
         <v>36</v>
       </c>
@@ -1496,7 +1502,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C24" s="5" t="s">
         <v>23</v>
       </c>
@@ -1504,7 +1510,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C25" s="5" t="s">
         <v>40</v>
       </c>
@@ -1518,7 +1524,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>50</v>
       </c>
@@ -1535,7 +1541,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C27" s="5" t="s">
         <v>53</v>
       </c>
@@ -1546,7 +1552,7 @@
         <v>15101</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C28" s="5" t="s">
         <v>55</v>
       </c>
@@ -1557,7 +1563,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C29" s="5" t="s">
         <v>61</v>
       </c>
@@ -1571,7 +1577,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>13</v>
       </c>
@@ -1582,7 +1588,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C31" s="5" t="s">
         <v>66</v>
       </c>
@@ -1594,7 +1600,7 @@
       </c>
       <c r="M31" s="2"/>
     </row>
-    <row r="32" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>13</v>
       </c>
@@ -1605,7 +1611,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C33" s="5" t="s">
         <v>118</v>
       </c>
@@ -1625,7 +1631,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C34" s="5" t="s">
         <v>133</v>
       </c>
@@ -1639,7 +1645,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C35" s="14" t="s">
         <v>136</v>
       </c>
@@ -1657,7 +1663,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>13</v>
       </c>
@@ -1675,7 +1681,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C37" s="5" t="s">
         <v>140</v>
       </c>
@@ -1686,7 +1692,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C38" s="5" t="s">
         <v>142</v>
       </c>
@@ -1697,7 +1703,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C39" s="5" t="s">
         <v>146</v>
       </c>
@@ -1705,12 +1711,12 @@
         <v>145</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C40" s="5" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C41" s="5" t="s">
         <v>149</v>
       </c>
@@ -1718,7 +1724,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C42" s="5" t="s">
         <v>183</v>
       </c>
@@ -1729,7 +1735,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>184</v>
       </c>
@@ -1743,7 +1749,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C45" s="5" t="s">
         <v>187</v>
       </c>
@@ -1754,7 +1760,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C46" s="5" t="s">
         <v>188</v>
       </c>
@@ -1765,7 +1771,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C47" s="5" t="s">
         <v>192</v>
       </c>
@@ -1776,40 +1782,29 @@
         <v>450</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C48" s="5" t="s">
         <v>194</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="J48">
-        <v>2</v>
-      </c>
-      <c r="K48">
-        <v>29.56</v>
-      </c>
-      <c r="L48">
-        <f>J48*K48</f>
-        <v>59.12</v>
-      </c>
-    </row>
-    <row r="49" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J49">
-        <v>3</v>
-      </c>
-      <c r="K49">
-        <v>104.34</v>
-      </c>
-      <c r="L49">
-        <f>J49*K49</f>
-        <v>313.02</v>
-      </c>
-    </row>
-    <row r="58" spans="10:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C50" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="E50">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="58" spans="3:11" x14ac:dyDescent="0.3">
       <c r="K58" s="2"/>
     </row>
-    <row r="113" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="113" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N113" s="6"/>
     </row>
   </sheetData>
@@ -1823,20 +1818,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A3E3F36-FCD2-4D59-81CE-AA1D1D1D0627}">
   <dimension ref="A1:N48"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B1">
         <v>0</v>
       </c>
@@ -1848,7 +1843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B2">
         <v>22</v>
       </c>
@@ -1870,7 +1865,7 @@
         <v>1614.08</v>
       </c>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>100</v>
       </c>
@@ -1892,7 +1887,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>5</v>
       </c>
@@ -1914,7 +1909,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="7">
         <f>SUM(B1:B4)</f>
         <v>127</v>
@@ -1940,16 +1935,16 @@
         <v>3414.08</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C6" s="9"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D7" s="9">
         <f>D5/B5</f>
         <v>813.24629921259839</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9">
         <f>B5-F5</f>
         <v>123</v>
@@ -1959,13 +1954,13 @@
         <v>99868.2</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D11" s="9">
         <f>D9/B9</f>
         <v>811.9365853658536</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="16">
         <v>1110104</v>
       </c>
@@ -1977,7 +1972,7 @@
         <v>1128432.67</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>57</v>
       </c>
@@ -2001,7 +1996,7 @@
         <v>1165892.92</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>58</v>
       </c>
@@ -2021,7 +2016,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B17" s="11" t="s">
         <v>59</v>
       </c>
@@ -2038,7 +2033,7 @@
       </c>
       <c r="H17" s="12"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
       <c r="G18" s="15">
@@ -2047,16 +2042,16 @@
       <c r="J18" s="9"/>
       <c r="K18" s="13"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="K19" s="6"/>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
       <c r="G21" s="6"/>
@@ -2065,7 +2060,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D22" s="6"/>
       <c r="E22" s="2"/>
       <c r="H22" s="13"/>
@@ -2073,24 +2068,24 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="G23" s="2"/>
       <c r="N23">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N24">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F25" s="6"/>
       <c r="N25">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="6"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -2098,113 +2093,113 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N27">
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N28">
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N29">
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F30" s="9"/>
       <c r="N30">
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N31">
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N32">
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N33">
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N34">
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N35">
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N36">
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N37">
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N38">
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N39">
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N40">
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N41">
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N42">
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N43">
         <v>30</v>
       </c>
     </row>
-    <row r="44" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N44">
         <v>30</v>
       </c>
     </row>
-    <row r="45" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N45">
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N46">
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N47">
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N48">
         <f>SUM(N21:N47)</f>
         <v>524</v>
@@ -2219,16 +2214,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BA96DCF-5607-4643-8615-E51DE316F486}">
   <dimension ref="A1:J162"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1">
         <v>310000085</v>
       </c>
@@ -2252,7 +2247,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>310000084</v>
       </c>
@@ -2280,7 +2275,7 @@
         <v>2850</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>310000083</v>
       </c>
@@ -2308,7 +2303,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>310000082</v>
       </c>
@@ -2336,7 +2331,7 @@
         <v>2091</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>310000081</v>
       </c>
@@ -2364,7 +2359,7 @@
         <v>9900</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>310000081</v>
       </c>
@@ -2392,7 +2387,7 @@
         <v>652.1739</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>310000080</v>
       </c>
@@ -2420,7 +2415,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>310000079</v>
       </c>
@@ -2448,7 +2443,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>310000078</v>
       </c>
@@ -2476,7 +2471,7 @@
         <v>3015</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>310000077</v>
       </c>
@@ -2504,7 +2499,7 @@
         <v>50400</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>310000076</v>
       </c>
@@ -2532,7 +2527,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>310000075</v>
       </c>
@@ -2560,7 +2555,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>310000071</v>
       </c>
@@ -2588,7 +2583,7 @@
         <v>8350</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>310000069</v>
       </c>
@@ -2616,7 +2611,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>310000066</v>
       </c>
@@ -2644,7 +2639,7 @@
         <v>2520</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>310000065</v>
       </c>
@@ -2672,7 +2667,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>310000059</v>
       </c>
@@ -2700,7 +2695,7 @@
         <v>365.21999999999997</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>310000058</v>
       </c>
@@ -2728,7 +2723,7 @@
         <v>504.36</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>310000056</v>
       </c>
@@ -2756,7 +2751,7 @@
         <v>434.8</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>310000055</v>
       </c>
@@ -2784,7 +2779,7 @@
         <v>326.08499999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>310000054</v>
       </c>
@@ -2812,7 +2807,7 @@
         <v>326.09250000000003</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>310000054</v>
       </c>
@@ -2840,7 +2835,7 @@
         <v>22.61</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>310000054</v>
       </c>
@@ -2868,7 +2863,7 @@
         <v>104.34</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>310000053</v>
       </c>
@@ -2896,7 +2891,7 @@
         <v>339.12</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>310000051</v>
       </c>
@@ -2924,7 +2919,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>310000050</v>
       </c>
@@ -2952,7 +2947,7 @@
         <v>208.70999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>310000045</v>
       </c>
@@ -2980,7 +2975,7 @@
         <v>1664.88</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>310000044</v>
       </c>
@@ -3008,7 +3003,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>310000043</v>
       </c>
@@ -3036,7 +3031,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>310000042</v>
       </c>
@@ -3064,7 +3059,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>310000041</v>
       </c>
@@ -3092,7 +3087,7 @@
         <v>330.44</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>310000040</v>
       </c>
@@ -3120,7 +3115,7 @@
         <v>1236.9960000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>310000039</v>
       </c>
@@ -3148,7 +3143,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>310000038</v>
       </c>
@@ -3176,7 +3171,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>310000036</v>
       </c>
@@ -3204,7 +3199,7 @@
         <v>2874</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>310000036</v>
       </c>
@@ -3232,7 +3227,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>310000035</v>
       </c>
@@ -3260,7 +3255,7 @@
         <v>3200</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>310000033</v>
       </c>
@@ -3288,7 +3283,7 @@
         <v>3304.5709999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>310000026</v>
       </c>
@@ -3316,7 +3311,7 @@
         <v>3902</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>310000025</v>
       </c>
@@ -3344,7 +3339,7 @@
         <v>13650</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>310000025</v>
       </c>
@@ -3372,7 +3367,7 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>310000024</v>
       </c>
@@ -3400,7 +3395,7 @@
         <v>5923.36</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>310000023</v>
       </c>
@@ -3428,7 +3423,7 @@
         <v>732.08600000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>310000023</v>
       </c>
@@ -3456,7 +3451,7 @@
         <v>11526.3</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>310000021</v>
       </c>
@@ -3484,7 +3479,7 @@
         <v>10750</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>310000020</v>
       </c>
@@ -3512,7 +3507,7 @@
         <v>170275</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>310000019</v>
       </c>
@@ -3540,7 +3535,7 @@
         <v>24925</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>310000018</v>
       </c>
@@ -3568,7 +3563,7 @@
         <v>39683.600000000006</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>310000017</v>
       </c>
@@ -3596,7 +3591,7 @@
         <v>15522</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>310000016</v>
       </c>
@@ -3624,7 +3619,7 @@
         <v>47355</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>310000015</v>
       </c>
@@ -3643,7 +3638,7 @@
         <v>477584.74439999997</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>310000014</v>
       </c>
@@ -3658,7 +3653,7 @@
         <v>3200</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>310000014</v>
       </c>
@@ -3673,7 +3668,7 @@
         <v>19932</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>310000013</v>
       </c>
@@ -3688,7 +3683,7 @@
         <v>9755</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>310000012</v>
       </c>
@@ -3703,7 +3698,7 @@
         <v>27300</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>310000011</v>
       </c>
@@ -3718,7 +3713,7 @@
         <v>32000</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>310000010</v>
       </c>
@@ -3733,7 +3728,7 @@
         <v>10880</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>310000010</v>
       </c>
@@ -3748,7 +3743,7 @@
         <v>74042</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>310000009</v>
       </c>
@@ -3763,7 +3758,7 @@
         <v>20363.129999999997</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>310000007</v>
       </c>
@@ -3778,7 +3773,7 @@
         <v>80704</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>310000007</v>
       </c>
@@ -3793,7 +3788,7 @@
         <v>18078.28</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>310000006</v>
       </c>
@@ -3808,7 +3803,7 @@
         <v>89225</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>310000005</v>
       </c>
@@ -3823,7 +3818,7 @@
         <v>111300</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>310000005</v>
       </c>
@@ -3842,7 +3837,7 @@
         <v>900208.41800000006</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>310000004</v>
       </c>
@@ -3857,7 +3852,7 @@
         <v>46859</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>310000003</v>
       </c>
@@ -3872,7 +3867,7 @@
         <v>64999.000000000007</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>310000002</v>
       </c>
@@ -3887,7 +3882,7 @@
         <v>78804</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>310000001</v>
       </c>
@@ -3902,13 +3897,13 @@
         <v>192495</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D69" s="6">
         <f>SUM(D1:D68)</f>
         <v>1377793.1624</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H72">
         <v>-3300</v>
       </c>
@@ -3916,7 +3911,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B73" s="6"/>
       <c r="H73">
         <v>-2091</v>
@@ -3925,7 +3920,7 @@
         <v>22.61</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H74">
         <v>20</v>
       </c>
@@ -3933,7 +3928,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H75">
         <v>22.61</v>
       </c>
@@ -3941,7 +3936,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H76">
         <v>100</v>
       </c>
@@ -3949,7 +3944,7 @@
         <v>104.34</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H77">
         <v>100</v>
       </c>
@@ -3957,7 +3952,7 @@
         <v>121.74</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H78">
         <v>104.34</v>
       </c>
@@ -3965,7 +3960,7 @@
         <v>121.74</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H79">
         <v>121.74</v>
       </c>
@@ -3973,7 +3968,7 @@
         <v>121.74</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H80">
         <v>121.74</v>
       </c>
@@ -3981,7 +3976,7 @@
         <v>126.09</v>
       </c>
     </row>
-    <row r="81" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H81">
         <v>121.74</v>
       </c>
@@ -3989,7 +3984,7 @@
         <v>126.09</v>
       </c>
     </row>
-    <row r="82" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H82">
         <v>126.09</v>
       </c>
@@ -3997,7 +3992,7 @@
         <v>126.09</v>
       </c>
     </row>
-    <row r="83" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H83">
         <v>126.09</v>
       </c>
@@ -4005,7 +4000,7 @@
         <v>126.09</v>
       </c>
     </row>
-    <row r="84" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H84">
         <v>126.09</v>
       </c>
@@ -4013,7 +4008,7 @@
         <v>165.22</v>
       </c>
     </row>
-    <row r="85" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H85">
         <v>126.09</v>
       </c>
@@ -4021,7 +4016,7 @@
         <v>165.22</v>
       </c>
     </row>
-    <row r="86" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H86">
         <v>139.13999999999999</v>
       </c>
@@ -4029,7 +4024,7 @@
         <v>208.71</v>
       </c>
     </row>
-    <row r="87" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H87">
         <v>160</v>
       </c>
@@ -4037,7 +4032,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="88" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H88">
         <v>165.22</v>
       </c>
@@ -4045,7 +4040,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="89" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H89">
         <v>165.22</v>
       </c>
@@ -4053,7 +4048,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="90" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H90">
         <v>208.71</v>
       </c>
@@ -4061,7 +4056,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="91" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H91">
         <v>220</v>
       </c>
@@ -4069,7 +4064,7 @@
         <v>326.08499999999998</v>
       </c>
     </row>
-    <row r="92" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H92">
         <v>220</v>
       </c>
@@ -4077,7 +4072,7 @@
         <v>326.09249999999997</v>
       </c>
     </row>
-    <row r="93" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H93">
         <v>320</v>
       </c>
@@ -4085,7 +4080,7 @@
         <v>339.12</v>
       </c>
     </row>
-    <row r="94" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H94">
         <v>326.08499999999998</v>
       </c>
@@ -4093,7 +4088,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="95" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H95">
         <v>326.09249999999997</v>
       </c>
@@ -4101,7 +4096,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="96" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H96">
         <v>339.12</v>
       </c>
@@ -4109,7 +4104,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="97" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H97">
         <v>350</v>
       </c>
@@ -4117,7 +4112,7 @@
         <v>384.21</v>
       </c>
     </row>
-    <row r="98" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H98">
         <v>350</v>
       </c>
@@ -4125,7 +4120,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="99" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H99">
         <v>385</v>
       </c>
@@ -4133,7 +4128,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="100" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H100">
         <v>434.8</v>
       </c>
@@ -4141,7 +4136,7 @@
         <v>434.8</v>
       </c>
     </row>
-    <row r="101" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H101">
         <v>440</v>
       </c>
@@ -4149,7 +4144,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="102" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H102">
         <v>440</v>
       </c>
@@ -4157,7 +4152,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="103" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H103">
         <v>470</v>
       </c>
@@ -4165,7 +4160,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="104" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H104">
         <v>630</v>
       </c>
@@ -4173,7 +4168,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="105" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H105">
         <v>630</v>
       </c>
@@ -4181,7 +4176,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="106" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H106">
         <v>652.1739</v>
       </c>
@@ -4189,7 +4184,7 @@
         <v>652.1739</v>
       </c>
     </row>
-    <row r="107" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H107">
         <v>663.66600000000005</v>
       </c>
@@ -4197,7 +4192,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="108" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H108">
         <v>675</v>
       </c>
@@ -4205,7 +4200,7 @@
         <v>684.2</v>
       </c>
     </row>
-    <row r="109" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H109">
         <v>750</v>
       </c>
@@ -4213,7 +4208,7 @@
         <v>732.08600000000001</v>
       </c>
     </row>
-    <row r="110" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H110">
         <v>790</v>
       </c>
@@ -4221,7 +4216,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="111" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H111">
         <v>840</v>
       </c>
@@ -4229,7 +4224,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="112" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H112">
         <v>880</v>
       </c>
@@ -4237,7 +4232,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="113" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H113">
         <v>900</v>
       </c>
@@ -4245,7 +4240,7 @@
         <v>832.44</v>
       </c>
     </row>
-    <row r="114" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H114">
         <v>912</v>
       </c>
@@ -4253,7 +4248,7 @@
         <v>832.44</v>
       </c>
     </row>
-    <row r="115" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H115">
         <v>1236.9960000000001</v>
       </c>
@@ -4261,7 +4256,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="116" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H116">
         <v>1260</v>
       </c>
@@ -4269,7 +4264,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="117" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H117">
         <v>1260</v>
       </c>
@@ -4277,7 +4272,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="118" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H118">
         <v>1260</v>
       </c>
@@ -4285,7 +4280,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="119" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H119">
         <v>1750</v>
       </c>
@@ -4293,7 +4288,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="120" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H120">
         <v>1800</v>
       </c>
@@ -4301,7 +4296,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="121" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H121">
         <v>1908</v>
       </c>
@@ -4309,7 +4304,7 @@
         <v>1236.9960000000001</v>
       </c>
     </row>
-    <row r="122" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="122" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H122">
         <v>2091</v>
       </c>
@@ -4317,7 +4312,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="123" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="123" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H123">
         <v>2091</v>
       </c>
@@ -4325,7 +4320,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="124" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="124" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H124">
         <v>2640</v>
       </c>
@@ -4333,7 +4328,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="125" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H125">
         <v>2874</v>
       </c>
@@ -4341,7 +4336,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="126" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H126">
         <v>3015</v>
       </c>
@@ -4349,7 +4344,7 @@
         <v>1921.05</v>
       </c>
     </row>
-    <row r="127" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H127">
         <v>3200</v>
       </c>
@@ -4357,7 +4352,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="128" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H128">
         <v>3300</v>
       </c>
@@ -4365,7 +4360,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="129" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H129">
         <v>3300</v>
       </c>
@@ -4373,7 +4368,7 @@
         <v>2091</v>
       </c>
     </row>
-    <row r="130" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H130">
         <v>4000</v>
       </c>
@@ -4381,7 +4376,7 @@
         <v>2850</v>
       </c>
     </row>
-    <row r="131" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="131" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H131">
         <v>4080</v>
       </c>
@@ -4389,7 +4384,7 @@
         <v>2991</v>
       </c>
     </row>
-    <row r="132" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H132">
         <v>4550</v>
       </c>
@@ -4397,7 +4392,7 @@
         <v>3015</v>
       </c>
     </row>
-    <row r="133" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="133" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H133">
         <v>5040</v>
       </c>
@@ -4405,7 +4400,7 @@
         <v>3200</v>
       </c>
     </row>
-    <row r="134" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="134" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H134">
         <v>6600</v>
       </c>
@@ -4413,7 +4408,7 @@
         <v>3300</v>
       </c>
     </row>
-    <row r="135" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="135" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H135">
         <v>7500</v>
       </c>
@@ -4421,7 +4416,7 @@
         <v>3304.5709999999999</v>
       </c>
     </row>
-    <row r="136" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="136" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H136">
         <v>7500</v>
       </c>
@@ -4429,7 +4424,7 @@
         <v>3582</v>
       </c>
     </row>
-    <row r="137" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="137" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H137">
         <v>7560</v>
       </c>
@@ -4437,7 +4432,7 @@
         <v>3690</v>
       </c>
     </row>
-    <row r="138" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="138" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H138">
         <v>8058.9989999999998</v>
       </c>
@@ -4445,7 +4440,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="139" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="139" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H139">
         <v>8350</v>
       </c>
@@ -4453,7 +4448,7 @@
         <v>4550</v>
       </c>
     </row>
-    <row r="140" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="140" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H140">
         <v>9600</v>
       </c>
@@ -4461,7 +4456,7 @@
         <v>4789.3999999999996</v>
       </c>
     </row>
-    <row r="141" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="141" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H141">
         <v>9755</v>
       </c>
@@ -4469,7 +4464,7 @@
         <v>4985</v>
       </c>
     </row>
-    <row r="142" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H142">
         <v>10880</v>
       </c>
@@ -4477,7 +4472,7 @@
         <v>5923.36</v>
       </c>
     </row>
-    <row r="143" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="143" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H143">
         <v>11400</v>
       </c>
@@ -4485,7 +4480,7 @@
         <v>5982</v>
       </c>
     </row>
-    <row r="144" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="144" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H144">
         <v>18078.28</v>
       </c>
@@ -4493,7 +4488,7 @@
         <v>6600</v>
       </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>119</v>
       </c>
@@ -4516,7 +4511,7 @@
         <v>6979</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>112</v>
       </c>
@@ -4543,7 +4538,7 @@
         <v>8350</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>112</v>
       </c>
@@ -4574,7 +4569,7 @@
         <v>9100</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>112</v>
       </c>
@@ -4605,7 +4600,7 @@
         <v>9221.0400000000009</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>112</v>
       </c>
@@ -4628,7 +4623,7 @@
         <v>10750</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>112</v>
       </c>
@@ -4651,7 +4646,7 @@
         <v>11940</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>112</v>
       </c>
@@ -4674,7 +4669,7 @@
         <v>12300</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>112</v>
       </c>
@@ -4697,7 +4692,7 @@
         <v>12510</v>
       </c>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>112</v>
       </c>
@@ -4720,7 +4715,7 @@
         <v>17375</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D154">
         <f>SUM(D146:D153)</f>
         <v>704</v>
@@ -4732,7 +4727,7 @@
         <v>20850</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H155">
         <v>80704</v>
       </c>
@@ -4740,7 +4735,7 @@
         <v>22240</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H156">
         <v>83244</v>
       </c>
@@ -4748,7 +4743,7 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H157">
         <v>89225</v>
       </c>
@@ -4756,7 +4751,7 @@
         <v>27800</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H158">
         <v>111300</v>
       </c>
@@ -4764,7 +4759,7 @@
         <v>30750</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H159">
         <v>192495</v>
       </c>
@@ -4772,7 +4767,7 @@
         <v>34210</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H160">
         <v>208500</v>
       </c>
@@ -4780,7 +4775,7 @@
         <v>50400</v>
       </c>
     </row>
-    <row r="161" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="161" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H161" s="8">
         <f>SUM(H72:H160)</f>
         <v>1377793.1624</v>
@@ -4789,7 +4784,7 @@
         <v>69500</v>
       </c>
     </row>
-    <row r="162" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="162" spans="8:10" x14ac:dyDescent="0.3">
       <c r="J162" s="6">
         <f>SUM(J72:J161)</f>
         <v>477584.74439999997</v>
@@ -4803,9 +4798,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A1A91D3-643F-4BB9-8D03-CCEBAAE4D8FC}">
   <dimension ref="A1:I429"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1">
         <v>1</v>
       </c>
@@ -4817,7 +4812,7 @@
         <v>504.3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4829,7 +4824,7 @@
         <v>504.3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -4841,7 +4836,7 @@
         <v>504.3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -4853,7 +4848,7 @@
         <v>504.3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -4865,7 +4860,7 @@
         <v>504.3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -4877,7 +4872,7 @@
         <v>504.3</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -4889,7 +4884,7 @@
         <v>504.3</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -4901,7 +4896,7 @@
         <v>504.3</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1</v>
       </c>
@@ -4913,7 +4908,7 @@
         <v>504.3</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1</v>
       </c>
@@ -4925,7 +4920,7 @@
         <v>504.3</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1</v>
       </c>
@@ -4937,7 +4932,7 @@
         <v>504.3</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>SUM(A1:A11)</f>
         <v>11</v>
@@ -4947,7 +4942,7 @@
         <v>5547.3000000000011</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2</v>
       </c>
@@ -4959,7 +4954,7 @@
         <v>1008.6</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -4971,7 +4966,7 @@
         <v>1008.6</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>4</v>
       </c>
@@ -4983,7 +4978,7 @@
         <v>2017.2</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2</v>
       </c>
@@ -4995,7 +4990,7 @@
         <v>1008.6</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1</v>
       </c>
@@ -5007,7 +5002,7 @@
         <v>504.3</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>SUM(A13:A17)</f>
         <v>11</v>
@@ -5017,7 +5012,7 @@
         <v>5547.3</v>
       </c>
     </row>
-    <row r="421" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="421" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F421" t="s">
         <v>179</v>
       </c>
@@ -5028,7 +5023,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="422" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="422" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F422">
         <v>100</v>
       </c>
@@ -5040,7 +5035,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="423" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="423" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F423">
         <v>100</v>
       </c>
@@ -5052,7 +5047,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="424" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="424" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F424">
         <v>-50</v>
       </c>
@@ -5064,7 +5059,7 @@
         <v>-5000</v>
       </c>
     </row>
-    <row r="425" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="425" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F425">
         <v>-100</v>
       </c>
@@ -5076,7 +5071,7 @@
         <v>-20000</v>
       </c>
     </row>
-    <row r="427" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="427" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F427">
         <f>SUM(F422:F426)</f>
         <v>50</v>
@@ -5086,7 +5081,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="429" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="429" spans="6:9" x14ac:dyDescent="0.3">
       <c r="I429" s="18">
         <f>H427/F427</f>
         <v>100</v>
